--- a/config/配置_v2.0.xlsx
+++ b/config/配置_v2.0.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="22981" windowHeight="11268"/>
+    <workbookView windowWidth="18569" windowHeight="11268" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="project" sheetId="1" r:id="rId1"/>
@@ -80,7 +80,7 @@
     <t>mqtt_host</t>
   </si>
   <si>
-    <t>192.168.100.155</t>
+    <t>118.193.44.31</t>
   </si>
   <si>
     <t>MQTT服务器地址</t>
@@ -924,7 +924,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -932,9 +932,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1318,127 +1315,127 @@
   <dimension ref="A1:C11"/>
   <sheetFormatPr defaultColWidth="22.4017094017094" defaultRowHeight="18" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="16384" width="22.4017094017094" style="4"/>
+    <col min="1" max="16384" width="22.4017094017094" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="3">
         <v>8083</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="4">
-        <v>1883</v>
-      </c>
-      <c r="C7" s="4" t="s">
+      <c r="B7" s="3">
+        <v>10031</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="3" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="3" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1455,101 +1452,101 @@
   <dimension ref="A1:E8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelRow="7" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="6.46153846153846" style="4" customWidth="1"/>
-    <col min="2" max="2" width="20.9316239316239" style="4" customWidth="1"/>
-    <col min="3" max="3" width="20.3333333333333" style="4" customWidth="1"/>
-    <col min="4" max="16384" width="9" style="4"/>
+    <col min="1" max="1" width="6.46153846153846" style="3" customWidth="1"/>
+    <col min="2" max="2" width="20.9316239316239" style="3" customWidth="1"/>
+    <col min="3" max="3" width="20.3333333333333" style="3" customWidth="1"/>
+    <col min="4" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" s="5" customFormat="1" spans="1:5">
-      <c r="A1" s="5" t="s">
+    <row r="1" s="4" customFormat="1" spans="1:5">
+      <c r="A1" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E1" s="4"/>
+      <c r="E1" s="3"/>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="4">
+      <c r="A2" s="3">
         <v>0</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="4">
+      <c r="A3" s="3">
         <v>1</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="4">
+      <c r="A4" s="3">
         <v>2</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="4">
+      <c r="A5" s="3">
         <v>3</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="4">
+      <c r="A6" s="3">
         <v>4</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="4">
+      <c r="A7" s="3">
         <v>5</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="4">
+      <c r="A8" s="3">
         <v>6</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>46</v>
       </c>
     </row>
@@ -1566,325 +1563,325 @@
   <dimension ref="A1:Q8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelRow="7"/>
   <cols>
-    <col min="1" max="1" width="6.46153846153846" style="4" customWidth="1"/>
-    <col min="2" max="2" width="15.5982905982906" style="4" customWidth="1"/>
-    <col min="3" max="3" width="13.4615384615385" style="4" customWidth="1"/>
-    <col min="4" max="4" width="12.9316239316239" style="4" customWidth="1"/>
-    <col min="5" max="5" width="23.7692307692308" style="4" customWidth="1"/>
-    <col min="6" max="10" width="12.1965811965812" style="4" customWidth="1"/>
-    <col min="11" max="11" width="16.6666666666667" style="4" customWidth="1"/>
-    <col min="12" max="16" width="12.1965811965812" style="4" customWidth="1"/>
-    <col min="17" max="16384" width="9.06837606837607" style="4"/>
+    <col min="1" max="1" width="6.46153846153846" style="3" customWidth="1"/>
+    <col min="2" max="2" width="15.5982905982906" style="3" customWidth="1"/>
+    <col min="3" max="3" width="13.4615384615385" style="3" customWidth="1"/>
+    <col min="4" max="4" width="12.9316239316239" style="3" customWidth="1"/>
+    <col min="5" max="5" width="23.7692307692308" style="3" customWidth="1"/>
+    <col min="6" max="10" width="12.1965811965812" style="3" customWidth="1"/>
+    <col min="11" max="11" width="16.6666666666667" style="3" customWidth="1"/>
+    <col min="12" max="16" width="12.1965811965812" style="3" customWidth="1"/>
+    <col min="17" max="16384" width="9.06837606837607" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" s="5" customFormat="1" spans="1:17">
-      <c r="A1" s="5" t="s">
+    <row r="1" s="4" customFormat="1" spans="1:17">
+      <c r="A1" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="K1" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="L1" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="M1" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="N1" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="O1" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="P1" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="Q1" s="4" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:17">
-      <c r="A2" s="4">
+      <c r="A2" s="3">
         <f>devices!A2</f>
         <v>0</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F2" s="4">
+      <c r="F2" s="3">
         <v>1000</v>
       </c>
-      <c r="G2" s="4">
+      <c r="G2" s="3">
         <v>500</v>
       </c>
-      <c r="L2" s="4">
+      <c r="L2" s="3">
         <v>500000</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="P2" s="3" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:17">
-      <c r="A3" s="4">
+      <c r="A3" s="3">
         <f>devices!A3</f>
         <v>1</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F3" s="3">
         <v>1000</v>
       </c>
-      <c r="G3" s="4">
+      <c r="G3" s="3">
         <v>500</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I3" s="4">
+      <c r="I3" s="3">
         <v>33434</v>
       </c>
-      <c r="J3" s="4">
+      <c r="J3" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:17">
-      <c r="A4" s="4">
+      <c r="A4" s="3">
         <f>devices!A4</f>
         <v>2</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="3">
         <v>1000</v>
       </c>
-      <c r="G4" s="4">
+      <c r="G4" s="3">
         <v>500</v>
       </c>
-      <c r="J4" s="4">
+      <c r="J4" s="3">
         <v>1</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="K4" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="L4" s="4">
+      <c r="L4" s="3">
         <v>9600</v>
       </c>
-      <c r="M4" s="4">
+      <c r="M4" s="3">
         <v>8</v>
       </c>
-      <c r="N4" s="4" t="s">
+      <c r="N4" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="O4" s="4">
+      <c r="O4" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:17">
-      <c r="A5" s="4">
+      <c r="A5" s="3">
         <f>devices!A5</f>
         <v>3</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="3">
         <v>1000</v>
       </c>
-      <c r="G5" s="4">
+      <c r="G5" s="3">
         <v>500</v>
       </c>
-      <c r="J5" s="4">
+      <c r="J5" s="3">
         <v>1</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="K5" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="L5" s="4">
+      <c r="L5" s="3">
         <v>9600</v>
       </c>
-      <c r="M5" s="4">
+      <c r="M5" s="3">
         <v>8</v>
       </c>
-      <c r="N5" s="4" t="s">
+      <c r="N5" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="O5" s="4">
+      <c r="O5" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:17">
-      <c r="A6" s="4">
+      <c r="A6" s="3">
         <f>devices!A6</f>
         <v>4</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="3">
         <v>1000</v>
       </c>
-      <c r="G6" s="4">
+      <c r="G6" s="3">
         <v>500</v>
       </c>
-      <c r="J6" s="4">
+      <c r="J6" s="3">
         <v>1</v>
       </c>
-      <c r="K6" s="4" t="s">
+      <c r="K6" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="L6" s="4">
+      <c r="L6" s="3">
         <v>9600</v>
       </c>
-      <c r="M6" s="4">
+      <c r="M6" s="3">
         <v>8</v>
       </c>
-      <c r="N6" s="4" t="s">
+      <c r="N6" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="O6" s="4">
+      <c r="O6" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:17">
-      <c r="A7" s="4">
+      <c r="A7" s="3">
         <f>devices!A7</f>
         <v>5</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="3">
         <v>1000</v>
       </c>
-      <c r="G7" s="4">
+      <c r="G7" s="3">
         <v>500</v>
       </c>
-      <c r="J7" s="4">
+      <c r="J7" s="3">
         <v>1</v>
       </c>
-      <c r="K7" s="4" t="s">
+      <c r="K7" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="L7" s="4">
+      <c r="L7" s="3">
         <v>9600</v>
       </c>
-      <c r="M7" s="4">
+      <c r="M7" s="3">
         <v>8</v>
       </c>
-      <c r="N7" s="4" t="s">
+      <c r="N7" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="O7" s="4">
+      <c r="O7" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:17">
-      <c r="A8" s="4">
+      <c r="A8" s="3">
         <f>devices!A8</f>
         <v>6</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F8" s="4">
+      <c r="F8" s="3">
         <v>1000</v>
       </c>
-      <c r="G8" s="4">
+      <c r="G8" s="3">
         <v>500</v>
       </c>
-      <c r="J8" s="4">
+      <c r="J8" s="3">
         <v>1</v>
       </c>
-      <c r="K8" s="4" t="s">
+      <c r="K8" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="L8" s="4">
+      <c r="L8" s="3">
         <v>9600</v>
       </c>
-      <c r="M8" s="4">
+      <c r="M8" s="3">
         <v>8</v>
       </c>
-      <c r="N8" s="4" t="s">
+      <c r="N8" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="O8" s="4">
+      <c r="O8" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1911,10 +1908,10 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:7">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>71</v>
       </c>
       <c r="C1" s="1" t="s">
@@ -1931,7 +1928,7 @@
       <c r="A2" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>74</v>
       </c>
       <c r="C2" s="2" t="str">

--- a/config/配置_v2.0.xlsx
+++ b/config/配置_v2.0.xlsx
@@ -80,7 +80,7 @@
     <t>mqtt_host</t>
   </si>
   <si>
-    <t>118.193.44.31</t>
+    <t>192.168.100.155</t>
   </si>
   <si>
     <t>MQTT服务器地址</t>
@@ -221,7 +221,7 @@
     <t>ModbusTCP</t>
   </si>
   <si>
-    <t>./config/PCS_450.xlsx</t>
+    <t>./config/PCS_125_英博.xlsx</t>
   </si>
   <si>
     <t>ModbusRTU</t>
@@ -1030,6 +1030,886 @@
             <v>3</v>
           </cell>
         </row>
+        <row r="5">
+          <cell r="A5">
+            <v>4</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="A6">
+            <v>5</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="A7">
+            <v>6</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="A8">
+            <v>7</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="A9">
+            <v>8</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="A10">
+            <v>9</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="A11">
+            <v>10</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="A12">
+            <v>11</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="A13">
+            <v>12</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="A14">
+            <v>13</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="A15">
+            <v>14</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="A16">
+            <v>15</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="A17">
+            <v>16</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="A18">
+            <v>17</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="A19">
+            <v>18</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="A20">
+            <v>19</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="A21">
+            <v>20</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="A22">
+            <v>21</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="A23">
+            <v>22</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="A24">
+            <v>23</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="A25">
+            <v>24</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="A26">
+            <v>25</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="A27">
+            <v>26</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="A28">
+            <v>27</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="A29">
+            <v>28</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="A30">
+            <v>29</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="A31">
+            <v>30</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="A32">
+            <v>31</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="A33">
+            <v>32</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="A34">
+            <v>33</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="A35">
+            <v>34</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="A36">
+            <v>35</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="A37">
+            <v>36</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="A38">
+            <v>37</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="A39">
+            <v>38</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="A40">
+            <v>39</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="A41">
+            <v>40</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="A42">
+            <v>41</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="A43">
+            <v>42</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="A44">
+            <v>43</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="A45">
+            <v>44</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="A46">
+            <v>45</v>
+          </cell>
+        </row>
+        <row r="47">
+          <cell r="A47">
+            <v>46</v>
+          </cell>
+        </row>
+        <row r="48">
+          <cell r="A48">
+            <v>47</v>
+          </cell>
+        </row>
+        <row r="49">
+          <cell r="A49">
+            <v>48</v>
+          </cell>
+        </row>
+        <row r="50">
+          <cell r="A50">
+            <v>49</v>
+          </cell>
+        </row>
+        <row r="51">
+          <cell r="A51">
+            <v>50</v>
+          </cell>
+        </row>
+        <row r="52">
+          <cell r="A52">
+            <v>51</v>
+          </cell>
+        </row>
+        <row r="53">
+          <cell r="A53">
+            <v>52</v>
+          </cell>
+        </row>
+        <row r="54">
+          <cell r="A54">
+            <v>53</v>
+          </cell>
+        </row>
+        <row r="55">
+          <cell r="A55">
+            <v>54</v>
+          </cell>
+        </row>
+        <row r="56">
+          <cell r="A56">
+            <v>55</v>
+          </cell>
+        </row>
+        <row r="57">
+          <cell r="A57">
+            <v>56</v>
+          </cell>
+        </row>
+        <row r="58">
+          <cell r="A58">
+            <v>57</v>
+          </cell>
+        </row>
+        <row r="59">
+          <cell r="A59">
+            <v>58</v>
+          </cell>
+        </row>
+        <row r="60">
+          <cell r="A60">
+            <v>59</v>
+          </cell>
+        </row>
+        <row r="61">
+          <cell r="A61">
+            <v>60</v>
+          </cell>
+        </row>
+        <row r="62">
+          <cell r="A62">
+            <v>61</v>
+          </cell>
+        </row>
+        <row r="63">
+          <cell r="A63">
+            <v>62</v>
+          </cell>
+        </row>
+        <row r="64">
+          <cell r="A64">
+            <v>63</v>
+          </cell>
+        </row>
+        <row r="65">
+          <cell r="A65">
+            <v>64</v>
+          </cell>
+        </row>
+        <row r="66">
+          <cell r="A66">
+            <v>65</v>
+          </cell>
+        </row>
+        <row r="67">
+          <cell r="A67">
+            <v>66</v>
+          </cell>
+        </row>
+        <row r="68">
+          <cell r="A68">
+            <v>67</v>
+          </cell>
+        </row>
+        <row r="69">
+          <cell r="A69">
+            <v>68</v>
+          </cell>
+        </row>
+        <row r="70">
+          <cell r="A70">
+            <v>69</v>
+          </cell>
+        </row>
+        <row r="71">
+          <cell r="A71">
+            <v>70</v>
+          </cell>
+        </row>
+        <row r="72">
+          <cell r="A72">
+            <v>71</v>
+          </cell>
+        </row>
+        <row r="73">
+          <cell r="A73">
+            <v>72</v>
+          </cell>
+        </row>
+        <row r="74">
+          <cell r="A74">
+            <v>73</v>
+          </cell>
+        </row>
+        <row r="75">
+          <cell r="A75">
+            <v>74</v>
+          </cell>
+        </row>
+        <row r="76">
+          <cell r="A76">
+            <v>75</v>
+          </cell>
+        </row>
+        <row r="77">
+          <cell r="A77">
+            <v>76</v>
+          </cell>
+        </row>
+        <row r="78">
+          <cell r="A78">
+            <v>77</v>
+          </cell>
+        </row>
+        <row r="79">
+          <cell r="A79">
+            <v>78</v>
+          </cell>
+        </row>
+        <row r="80">
+          <cell r="A80">
+            <v>79</v>
+          </cell>
+        </row>
+        <row r="81">
+          <cell r="A81">
+            <v>80</v>
+          </cell>
+        </row>
+        <row r="82">
+          <cell r="A82">
+            <v>81</v>
+          </cell>
+        </row>
+        <row r="83">
+          <cell r="A83">
+            <v>82</v>
+          </cell>
+        </row>
+        <row r="84">
+          <cell r="A84">
+            <v>83</v>
+          </cell>
+        </row>
+        <row r="85">
+          <cell r="A85">
+            <v>84</v>
+          </cell>
+        </row>
+        <row r="86">
+          <cell r="A86">
+            <v>85</v>
+          </cell>
+        </row>
+        <row r="87">
+          <cell r="A87">
+            <v>86</v>
+          </cell>
+        </row>
+        <row r="88">
+          <cell r="A88">
+            <v>87</v>
+          </cell>
+        </row>
+        <row r="89">
+          <cell r="A89">
+            <v>88</v>
+          </cell>
+        </row>
+        <row r="90">
+          <cell r="A90">
+            <v>89</v>
+          </cell>
+        </row>
+        <row r="91">
+          <cell r="A91">
+            <v>90</v>
+          </cell>
+        </row>
+        <row r="92">
+          <cell r="A92">
+            <v>91</v>
+          </cell>
+        </row>
+        <row r="93">
+          <cell r="A93">
+            <v>92</v>
+          </cell>
+        </row>
+        <row r="94">
+          <cell r="A94">
+            <v>93</v>
+          </cell>
+        </row>
+        <row r="95">
+          <cell r="A95">
+            <v>94</v>
+          </cell>
+        </row>
+        <row r="96">
+          <cell r="A96">
+            <v>95</v>
+          </cell>
+        </row>
+        <row r="97">
+          <cell r="A97">
+            <v>96</v>
+          </cell>
+        </row>
+        <row r="98">
+          <cell r="A98">
+            <v>97</v>
+          </cell>
+        </row>
+        <row r="99">
+          <cell r="A99">
+            <v>98</v>
+          </cell>
+        </row>
+        <row r="100">
+          <cell r="A100">
+            <v>99</v>
+          </cell>
+        </row>
+        <row r="101">
+          <cell r="A101">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="102">
+          <cell r="A102">
+            <v>101</v>
+          </cell>
+        </row>
+        <row r="103">
+          <cell r="A103">
+            <v>102</v>
+          </cell>
+        </row>
+        <row r="104">
+          <cell r="A104">
+            <v>103</v>
+          </cell>
+        </row>
+        <row r="105">
+          <cell r="A105">
+            <v>104</v>
+          </cell>
+        </row>
+        <row r="106">
+          <cell r="A106">
+            <v>105</v>
+          </cell>
+        </row>
+        <row r="107">
+          <cell r="A107">
+            <v>106</v>
+          </cell>
+        </row>
+        <row r="108">
+          <cell r="A108">
+            <v>107</v>
+          </cell>
+        </row>
+        <row r="109">
+          <cell r="A109">
+            <v>108</v>
+          </cell>
+        </row>
+        <row r="110">
+          <cell r="A110">
+            <v>109</v>
+          </cell>
+        </row>
+        <row r="111">
+          <cell r="A111">
+            <v>110</v>
+          </cell>
+        </row>
+        <row r="112">
+          <cell r="A112">
+            <v>111</v>
+          </cell>
+        </row>
+        <row r="113">
+          <cell r="A113">
+            <v>112</v>
+          </cell>
+        </row>
+        <row r="114">
+          <cell r="A114">
+            <v>113</v>
+          </cell>
+        </row>
+        <row r="115">
+          <cell r="A115">
+            <v>114</v>
+          </cell>
+        </row>
+        <row r="116">
+          <cell r="A116">
+            <v>115</v>
+          </cell>
+        </row>
+        <row r="117">
+          <cell r="A117">
+            <v>116</v>
+          </cell>
+        </row>
+        <row r="118">
+          <cell r="A118">
+            <v>117</v>
+          </cell>
+        </row>
+        <row r="119">
+          <cell r="A119">
+            <v>118</v>
+          </cell>
+        </row>
+        <row r="120">
+          <cell r="A120">
+            <v>119</v>
+          </cell>
+        </row>
+        <row r="121">
+          <cell r="A121">
+            <v>120</v>
+          </cell>
+        </row>
+        <row r="122">
+          <cell r="A122">
+            <v>121</v>
+          </cell>
+        </row>
+        <row r="123">
+          <cell r="A123">
+            <v>122</v>
+          </cell>
+        </row>
+        <row r="124">
+          <cell r="A124">
+            <v>123</v>
+          </cell>
+        </row>
+        <row r="125">
+          <cell r="A125">
+            <v>124</v>
+          </cell>
+        </row>
+        <row r="126">
+          <cell r="A126">
+            <v>125</v>
+          </cell>
+        </row>
+        <row r="127">
+          <cell r="A127">
+            <v>126</v>
+          </cell>
+        </row>
+        <row r="128">
+          <cell r="A128">
+            <v>127</v>
+          </cell>
+        </row>
+        <row r="129">
+          <cell r="A129">
+            <v>128</v>
+          </cell>
+        </row>
+        <row r="130">
+          <cell r="A130">
+            <v>129</v>
+          </cell>
+        </row>
+        <row r="131">
+          <cell r="A131">
+            <v>130</v>
+          </cell>
+        </row>
+        <row r="132">
+          <cell r="A132">
+            <v>131</v>
+          </cell>
+        </row>
+        <row r="133">
+          <cell r="A133">
+            <v>132</v>
+          </cell>
+        </row>
+        <row r="134">
+          <cell r="A134">
+            <v>133</v>
+          </cell>
+        </row>
+        <row r="135">
+          <cell r="A135">
+            <v>134</v>
+          </cell>
+        </row>
+        <row r="136">
+          <cell r="A136">
+            <v>135</v>
+          </cell>
+        </row>
+        <row r="137">
+          <cell r="A137">
+            <v>136</v>
+          </cell>
+        </row>
+        <row r="138">
+          <cell r="A138">
+            <v>137</v>
+          </cell>
+        </row>
+        <row r="139">
+          <cell r="A139">
+            <v>138</v>
+          </cell>
+        </row>
+        <row r="140">
+          <cell r="A140">
+            <v>139</v>
+          </cell>
+        </row>
+        <row r="141">
+          <cell r="A141">
+            <v>140</v>
+          </cell>
+        </row>
+        <row r="142">
+          <cell r="A142">
+            <v>141</v>
+          </cell>
+        </row>
+        <row r="143">
+          <cell r="A143">
+            <v>142</v>
+          </cell>
+        </row>
+        <row r="144">
+          <cell r="A144">
+            <v>143</v>
+          </cell>
+        </row>
+        <row r="145">
+          <cell r="A145">
+            <v>144</v>
+          </cell>
+        </row>
+        <row r="146">
+          <cell r="A146">
+            <v>145</v>
+          </cell>
+        </row>
+        <row r="147">
+          <cell r="A147">
+            <v>146</v>
+          </cell>
+        </row>
+        <row r="148">
+          <cell r="A148">
+            <v>147</v>
+          </cell>
+        </row>
+        <row r="149">
+          <cell r="A149">
+            <v>148</v>
+          </cell>
+        </row>
+        <row r="150">
+          <cell r="A150">
+            <v>149</v>
+          </cell>
+        </row>
+        <row r="151">
+          <cell r="A151">
+            <v>150</v>
+          </cell>
+        </row>
+        <row r="152">
+          <cell r="A152">
+            <v>151</v>
+          </cell>
+        </row>
+        <row r="153">
+          <cell r="A153">
+            <v>152</v>
+          </cell>
+        </row>
+        <row r="154">
+          <cell r="A154">
+            <v>153</v>
+          </cell>
+        </row>
+        <row r="155">
+          <cell r="A155">
+            <v>154</v>
+          </cell>
+        </row>
+        <row r="156">
+          <cell r="A156">
+            <v>155</v>
+          </cell>
+        </row>
+        <row r="157">
+          <cell r="A157">
+            <v>156</v>
+          </cell>
+        </row>
+        <row r="158">
+          <cell r="A158">
+            <v>157</v>
+          </cell>
+        </row>
+        <row r="159">
+          <cell r="A159">
+            <v>158</v>
+          </cell>
+        </row>
+        <row r="160">
+          <cell r="A160">
+            <v>159</v>
+          </cell>
+        </row>
+        <row r="161">
+          <cell r="A161">
+            <v>160</v>
+          </cell>
+        </row>
+        <row r="162">
+          <cell r="A162">
+            <v>161</v>
+          </cell>
+        </row>
+        <row r="163">
+          <cell r="A163">
+            <v>162</v>
+          </cell>
+        </row>
+        <row r="164">
+          <cell r="A164">
+            <v>163</v>
+          </cell>
+        </row>
+        <row r="165">
+          <cell r="A165">
+            <v>164</v>
+          </cell>
+        </row>
+        <row r="166">
+          <cell r="A166">
+            <v>165</v>
+          </cell>
+        </row>
+        <row r="167">
+          <cell r="A167">
+            <v>166</v>
+          </cell>
+        </row>
+        <row r="168">
+          <cell r="A168">
+            <v>167</v>
+          </cell>
+        </row>
+        <row r="169">
+          <cell r="A169">
+            <v>168</v>
+          </cell>
+        </row>
+        <row r="170">
+          <cell r="A170">
+            <v>169</v>
+          </cell>
+        </row>
+        <row r="171">
+          <cell r="A171">
+            <v>170</v>
+          </cell>
+        </row>
+        <row r="172">
+          <cell r="A172">
+            <v>171</v>
+          </cell>
+        </row>
+        <row r="173">
+          <cell r="A173">
+            <v>172</v>
+          </cell>
+        </row>
+        <row r="174">
+          <cell r="A174">
+            <v>173</v>
+          </cell>
+        </row>
+        <row r="175">
+          <cell r="A175">
+            <v>174</v>
+          </cell>
+        </row>
+        <row r="176">
+          <cell r="A176">
+            <v>175</v>
+          </cell>
+        </row>
+        <row r="177">
+          <cell r="A177">
+            <v>176</v>
+          </cell>
+        </row>
+        <row r="178">
+          <cell r="A178">
+            <v>177</v>
+          </cell>
+        </row>
+        <row r="179">
+          <cell r="A179">
+            <v>178</v>
+          </cell>
+        </row>
+        <row r="180">
+          <cell r="A180">
+            <v>179</v>
+          </cell>
+        </row>
       </sheetData>
       <sheetData sheetId="1">
         <row r="2">
@@ -1037,6 +1917,81 @@
             <v>1000</v>
           </cell>
         </row>
+        <row r="3">
+          <cell r="A3">
+            <v>1001</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="A4">
+            <v>1002</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="A5">
+            <v>1003</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="A6">
+            <v>1004</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="A7">
+            <v>1005</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="A8">
+            <v>1006</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="A9">
+            <v>1007</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="A10">
+            <v>1008</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="A11">
+            <v>1009</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="A12">
+            <v>1010</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="A13">
+            <v>1011</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="A14">
+            <v>1012</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="A15">
+            <v>1013</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="A16">
+            <v>1014</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="A17">
+            <v>1015</v>
+          </cell>
+        </row>
       </sheetData>
       <sheetData sheetId="2">
         <row r="2">
@@ -1044,6 +1999,216 @@
             <v>2000</v>
           </cell>
         </row>
+        <row r="3">
+          <cell r="A3">
+            <v>2001</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="A4">
+            <v>2002</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="A5">
+            <v>2003</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="A6">
+            <v>2004</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="A7">
+            <v>2005</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="A8">
+            <v>2006</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="A9">
+            <v>2007</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="A10">
+            <v>2008</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="A11">
+            <v>2009</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="A12">
+            <v>2010</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="A13">
+            <v>2011</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="A14">
+            <v>2012</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="A15">
+            <v>2013</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="A16">
+            <v>2014</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="A17">
+            <v>2015</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="A18">
+            <v>2016</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="A19">
+            <v>2017</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="A20">
+            <v>2018</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="A21">
+            <v>2019</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="A22">
+            <v>2020</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="A23">
+            <v>2021</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="A24">
+            <v>2022</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="A25">
+            <v>2023</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="A26">
+            <v>2024</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="A27">
+            <v>2025</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="A28">
+            <v>2026</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="A29">
+            <v>2027</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="A30">
+            <v>2028</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="A31">
+            <v>2029</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="A32">
+            <v>2030</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="A33">
+            <v>2031</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="A34">
+            <v>2032</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="A35">
+            <v>2033</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="A36">
+            <v>2034</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="A37">
+            <v>2035</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="A38">
+            <v>2036</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="A39">
+            <v>2037</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="A40">
+            <v>2038</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="A41">
+            <v>2039</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="A42">
+            <v>2040</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="A43">
+            <v>2041</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="A44">
+            <v>2042</v>
+          </cell>
+        </row>
       </sheetData>
       <sheetData sheetId="3">
         <row r="2">
@@ -1054,6 +2219,76 @@
         <row r="3">
           <cell r="A3">
             <v>3001</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="A4">
+            <v>3002</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="A5">
+            <v>3003</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="A6">
+            <v>3004</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="A7">
+            <v>3005</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="A8">
+            <v>3006</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="A9">
+            <v>3007</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="A10">
+            <v>3008</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="A11">
+            <v>3009</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="A12">
+            <v>3010</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="A13">
+            <v>3011</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="A14">
+            <v>3012</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="A15">
+            <v>3013</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="A16">
+            <v>3014</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="A17">
+            <v>3015</v>
           </cell>
         </row>
       </sheetData>
@@ -1389,7 +2624,7 @@
         <v>17</v>
       </c>
       <c r="B7" s="3">
-        <v>10031</v>
+        <v>1883</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>18</v>
@@ -1900,7 +3135,7 @@
   <cols>
     <col min="1" max="1" width="9.11111111111111" style="2"/>
     <col min="2" max="2" width="20.6752136752137" style="2" customWidth="1"/>
-    <col min="3" max="3" width="18.4529914529915" style="2" customWidth="1"/>
+    <col min="3" max="3" width="54.5470085470085" style="2" customWidth="1"/>
     <col min="4" max="4" width="20.3931623931624" style="2" customWidth="1"/>
     <col min="5" max="5" width="10.2905982905983" style="2" customWidth="1"/>
     <col min="6" max="6" width="10.4358974358974" style="2" customWidth="1"/>
@@ -1932,8 +3167,8 @@
         <v>74</v>
       </c>
       <c r="C2" s="2" t="str">
-        <f>_xlfn.TEXTJOIN(",",TRUE,[1]遥信!$A$2:$A$100)</f>
-        <v>1000</v>
+        <f>_xlfn.TEXTJOIN(",",TRUE,[1]遥信!$A$2:$A$1000)</f>
+        <v>1000,1001,1002,1003,1004,1005,1006,1007,1008,1009,1010,1011,1012,1013,1014,1015</v>
       </c>
       <c r="D2" s="2">
         <v>1</v>
@@ -1947,8 +3182,8 @@
         <v>75</v>
       </c>
       <c r="C3" s="2" t="str">
-        <f>_xlfn.TEXTJOIN(",",TRUE,[1]遥测!$A$2:$A$100)</f>
-        <v>1,2,3</v>
+        <f>_xlfn.TEXTJOIN(",",TRUE,[1]遥测!$A$2:$A$1000)</f>
+        <v>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23,24,25,26,27,28,29,30,31,32,33,34,35,36,37,38,39,40,41,42,43,44,45,46,47,48,49,50,51,52,53,54,55,56,57,58,59,60,61,62,63,64,65,66,67,68,69,70,71,72,73,74,75,76,77,78,79,80,81,82,83,84,85,86,87,88,89,90,91,92,93,94,95,96,97,98,99,100,101,102,103,104,105,106,107,108,109,110,111,112,113,114,115,116,117,118,119,120,121,122,123,124,125,126,127,128,129,130,131,132,133,134,135,136,137,138,139,140,141,142,143,144,145,146,147,148,149,150,151,152,153,154,155,156,157,158,159,160,161,162,163,164,165,166,167,168,169,170,171,172,173,174,175,176,177,178,179</v>
       </c>
       <c r="D3" s="2">
         <v>1</v>
@@ -1962,8 +3197,8 @@
         <v>76</v>
       </c>
       <c r="C4" s="2" t="str">
-        <f>_xlfn.TEXTJOIN(",",TRUE,[1]遥调!$A$2:$A$100)</f>
-        <v>2000</v>
+        <f>_xlfn.TEXTJOIN(",",TRUE,[1]遥调!$A$2:$A$1000)</f>
+        <v>2000,2001,2002,2003,2004,2005,2006,2007,2008,2009,2010,2011,2012,2013,2014,2015,2016,2017,2018,2019,2020,2021,2022,2023,2024,2025,2026,2027,2028,2029,2030,2031,2032,2033,2034,2035,2036,2037,2038,2039,2040,2041,2042</v>
       </c>
       <c r="D4" s="2">
         <v>1</v>
@@ -1977,8 +3212,8 @@
         <v>77</v>
       </c>
       <c r="C5" s="2" t="str">
-        <f>_xlfn.TEXTJOIN(",",TRUE,[1]遥控!$A$2:$A$100)</f>
-        <v>3000,3001</v>
+        <f>_xlfn.TEXTJOIN(",",TRUE,[1]遥控!$A$2:$A$1000)</f>
+        <v>3000,3001,3002,3003,3004,3005,3006,3007,3008,3009,3010,3011,3012,3013,3014,3015</v>
       </c>
       <c r="D5" s="2">
         <v>1</v>

--- a/config/配置_v2.0.xlsx
+++ b/config/配置_v2.0.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="18569" windowHeight="11268" activeTab="3"/>
+    <workbookView windowWidth="22010" windowHeight="12332" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="project" sheetId="1" r:id="rId1"/>

--- a/config/配置_v2.0.xlsx
+++ b/config/配置_v2.0.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="22010" windowHeight="12332" activeTab="2"/>
+    <workbookView windowWidth="18569" windowHeight="11268" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="project" sheetId="1" r:id="rId1"/>
@@ -2802,7 +2802,7 @@
     <col min="2" max="2" width="15.5982905982906" style="3" customWidth="1"/>
     <col min="3" max="3" width="13.4615384615385" style="3" customWidth="1"/>
     <col min="4" max="4" width="12.9316239316239" style="3" customWidth="1"/>
-    <col min="5" max="5" width="23.7692307692308" style="3" customWidth="1"/>
+    <col min="5" max="5" width="44.5299145299145" style="3" customWidth="1"/>
     <col min="6" max="10" width="12.1965811965812" style="3" customWidth="1"/>
     <col min="11" max="11" width="16.6666666666667" style="3" customWidth="1"/>
     <col min="12" max="16" width="12.1965811965812" style="3" customWidth="1"/>

--- a/config/配置_v2.0.xlsx
+++ b/config/配置_v2.0.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="18569" windowHeight="11268" activeTab="2"/>
+    <workbookView windowWidth="18519" windowHeight="10774"/>
   </bookViews>
   <sheets>
     <sheet name="project" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="81">
   <si>
     <t>key</t>
   </si>
@@ -65,163 +65,166 @@
     <t>ip</t>
   </si>
   <si>
+    <t>0.0.0.0</t>
+  </si>
+  <si>
+    <t>主机IP</t>
+  </si>
+  <si>
+    <t>port</t>
+  </si>
+  <si>
+    <t>主机端口</t>
+  </si>
+  <si>
+    <t>mqtt_host</t>
+  </si>
+  <si>
+    <t>192.168.100.155</t>
+  </si>
+  <si>
+    <t>MQTT服务器地址</t>
+  </si>
+  <si>
+    <t>mqtt_port</t>
+  </si>
+  <si>
+    <t>MQTT服务器端口</t>
+  </si>
+  <si>
+    <t>mqtt_username</t>
+  </si>
+  <si>
+    <t>root</t>
+  </si>
+  <si>
+    <t>MQTT用户名</t>
+  </si>
+  <si>
+    <t>mqtt_password</t>
+  </si>
+  <si>
+    <t>inpower</t>
+  </si>
+  <si>
+    <t>MQTT密码</t>
+  </si>
+  <si>
+    <t>mqtt_yt</t>
+  </si>
+  <si>
+    <t>/asw/+/+/yt</t>
+  </si>
+  <si>
+    <t>MQTT遥调</t>
+  </si>
+  <si>
+    <t>mqtt_yk</t>
+  </si>
+  <si>
+    <t>/asw/+/+/yk</t>
+  </si>
+  <si>
+    <t>MQTT遥控</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>desc</t>
+  </si>
+  <si>
+    <t>bcu1</t>
+  </si>
+  <si>
+    <t>BCU</t>
+  </si>
+  <si>
+    <t>pcs</t>
+  </si>
+  <si>
+    <t>PCS</t>
+  </si>
+  <si>
+    <t>liquidcool1</t>
+  </si>
+  <si>
+    <t>LiquidCool</t>
+  </si>
+  <si>
+    <t>liquidcool2</t>
+  </si>
+  <si>
+    <t>liquidcool3</t>
+  </si>
+  <si>
+    <t>firefighting</t>
+  </si>
+  <si>
+    <t>Firefighting</t>
+  </si>
+  <si>
+    <t>dehumidifier</t>
+  </si>
+  <si>
+    <t>Dehumidifier</t>
+  </si>
+  <si>
+    <t>comType</t>
+  </si>
+  <si>
+    <t>registerFile</t>
+  </si>
+  <si>
+    <t>interval</t>
+  </si>
+  <si>
+    <t>timeout</t>
+  </si>
+  <si>
+    <t>slave</t>
+  </si>
+  <si>
+    <t>serialTty</t>
+  </si>
+  <si>
+    <t>baudRate</t>
+  </si>
+  <si>
+    <t>dataBits</t>
+  </si>
+  <si>
+    <t>parity</t>
+  </si>
+  <si>
+    <t>stopBits</t>
+  </si>
+  <si>
+    <t>interface</t>
+  </si>
+  <si>
+    <t>CAN</t>
+  </si>
+  <si>
+    <t>./config/BCU_GOLD.xlsx</t>
+  </si>
+  <si>
+    <t>vcan0</t>
+  </si>
+  <si>
+    <t>ModbusTCP</t>
+  </si>
+  <si>
+    <t>./config/PCS_125_英博.xlsx</t>
+  </si>
+  <si>
     <t>127.0.0.1</t>
-  </si>
-  <si>
-    <t>主机IP</t>
-  </si>
-  <si>
-    <t>port</t>
-  </si>
-  <si>
-    <t>主机端口</t>
-  </si>
-  <si>
-    <t>mqtt_host</t>
-  </si>
-  <si>
-    <t>192.168.100.155</t>
-  </si>
-  <si>
-    <t>MQTT服务器地址</t>
-  </si>
-  <si>
-    <t>mqtt_port</t>
-  </si>
-  <si>
-    <t>MQTT服务器端口</t>
-  </si>
-  <si>
-    <t>mqtt_username</t>
-  </si>
-  <si>
-    <t>root</t>
-  </si>
-  <si>
-    <t>MQTT用户名</t>
-  </si>
-  <si>
-    <t>mqtt_password</t>
-  </si>
-  <si>
-    <t>inpower</t>
-  </si>
-  <si>
-    <t>MQTT密码</t>
-  </si>
-  <si>
-    <t>mqtt_yt</t>
-  </si>
-  <si>
-    <t>/asw/+/+/yt</t>
-  </si>
-  <si>
-    <t>MQTT遥调</t>
-  </si>
-  <si>
-    <t>mqtt_yk</t>
-  </si>
-  <si>
-    <t>/asw/+/+/yk</t>
-  </si>
-  <si>
-    <t>MQTT遥控</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>type</t>
-  </si>
-  <si>
-    <t>desc</t>
-  </si>
-  <si>
-    <t>bcu1</t>
-  </si>
-  <si>
-    <t>BCU</t>
-  </si>
-  <si>
-    <t>pcs</t>
-  </si>
-  <si>
-    <t>PCS</t>
-  </si>
-  <si>
-    <t>liquidcool1</t>
-  </si>
-  <si>
-    <t>LiquidCool</t>
-  </si>
-  <si>
-    <t>liquidcool2</t>
-  </si>
-  <si>
-    <t>liquidcool3</t>
-  </si>
-  <si>
-    <t>firefighting</t>
-  </si>
-  <si>
-    <t>Firefighting</t>
-  </si>
-  <si>
-    <t>dehumidifier</t>
-  </si>
-  <si>
-    <t>Dehumidifier</t>
-  </si>
-  <si>
-    <t>comType</t>
-  </si>
-  <si>
-    <t>registerFile</t>
-  </si>
-  <si>
-    <t>interval</t>
-  </si>
-  <si>
-    <t>timeout</t>
-  </si>
-  <si>
-    <t>slave</t>
-  </si>
-  <si>
-    <t>serialTty</t>
-  </si>
-  <si>
-    <t>baudRate</t>
-  </si>
-  <si>
-    <t>dataBits</t>
-  </si>
-  <si>
-    <t>parity</t>
-  </si>
-  <si>
-    <t>stopBits</t>
-  </si>
-  <si>
-    <t>interface</t>
-  </si>
-  <si>
-    <t>CAN</t>
-  </si>
-  <si>
-    <t>./config/BCU_GOLD.xlsx</t>
-  </si>
-  <si>
-    <t>vcan0</t>
-  </si>
-  <si>
-    <t>ModbusTCP</t>
-  </si>
-  <si>
-    <t>./config/PCS_125_英博.xlsx</t>
   </si>
   <si>
     <t>ModbusRTU</t>
@@ -2602,7 +2605,7 @@
         <v>12</v>
       </c>
       <c r="B5" s="3">
-        <v>8083</v>
+        <v>9091</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>13</v>
@@ -2916,7 +2919,7 @@
         <v>500</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>10</v>
+        <v>63</v>
       </c>
       <c r="I3" s="3">
         <v>33434</v>
@@ -2937,7 +2940,7 @@
         <v>40</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F4" s="3">
         <v>1000</v>
@@ -2949,7 +2952,7 @@
         <v>1</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L4" s="3">
         <v>9600</v>
@@ -2958,7 +2961,7 @@
         <v>8</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O4" s="3">
         <v>1</v>
@@ -2976,7 +2979,7 @@
         <v>40</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F5" s="3">
         <v>1000</v>
@@ -2988,7 +2991,7 @@
         <v>1</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="L5" s="3">
         <v>9600</v>
@@ -2997,7 +3000,7 @@
         <v>8</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O5" s="3">
         <v>1</v>
@@ -3015,7 +3018,7 @@
         <v>40</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F6" s="3">
         <v>1000</v>
@@ -3027,7 +3030,7 @@
         <v>1</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L6" s="3">
         <v>9600</v>
@@ -3036,7 +3039,7 @@
         <v>8</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O6" s="3">
         <v>1</v>
@@ -3054,7 +3057,7 @@
         <v>44</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F7" s="3">
         <v>1000</v>
@@ -3066,7 +3069,7 @@
         <v>1</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L7" s="3">
         <v>9600</v>
@@ -3075,7 +3078,7 @@
         <v>8</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O7" s="3">
         <v>1</v>
@@ -3093,7 +3096,7 @@
         <v>46</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F8" s="3">
         <v>1000</v>
@@ -3105,7 +3108,7 @@
         <v>1</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L8" s="3">
         <v>9600</v>
@@ -3114,7 +3117,7 @@
         <v>8</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O8" s="3">
         <v>1</v>
@@ -3144,16 +3147,16 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
@@ -3164,7 +3167,7 @@
         <v>37</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C2" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[1]遥信!$A$2:$A$1000)</f>
@@ -3179,7 +3182,7 @@
         <v>37</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C3" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[1]遥测!$A$2:$A$1000)</f>
@@ -3194,7 +3197,7 @@
         <v>37</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C4" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[1]遥调!$A$2:$A$1000)</f>
@@ -3209,7 +3212,7 @@
         <v>37</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C5" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[1]遥控!$A$2:$A$1000)</f>
@@ -3224,10 +3227,10 @@
         <v>35</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D6" s="2">
         <v>1</v>

--- a/config/配置_v2.0.xlsx
+++ b/config/配置_v2.0.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="18519" windowHeight="10774"/>
+    <workbookView windowWidth="18569" windowHeight="10825"/>
   </bookViews>
   <sheets>
     <sheet name="project" sheetId="1" r:id="rId1"/>
@@ -80,7 +80,7 @@
     <t>mqtt_host</t>
   </si>
   <si>
-    <t>192.168.100.155</t>
+    <t>60.204.207.155</t>
   </si>
   <si>
     <t>MQTT服务器地址</t>
@@ -2627,7 +2627,7 @@
         <v>17</v>
       </c>
       <c r="B7" s="3">
-        <v>1883</v>
+        <v>9131</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>18</v>

--- a/config/配置_v2.0.xlsx
+++ b/config/配置_v2.0.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="18569" windowHeight="10825"/>
+    <workbookView windowWidth="22010" windowHeight="12332"/>
   </bookViews>
   <sheets>
     <sheet name="project" sheetId="1" r:id="rId1"/>
@@ -14,6 +14,7 @@
   </sheets>
   <externalReferences>
     <externalReference r:id="rId5"/>
+    <externalReference r:id="rId6"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -221,7 +222,7 @@
     <t>ModbusTCP</t>
   </si>
   <si>
-    <t>./config/PCS_125_英博.xlsx</t>
+    <t>./config/PCS_英博_大机.xlsx</t>
   </si>
   <si>
     <t>127.0.0.1</t>
@@ -1017,985 +1018,8 @@
       <sheetName val="遥控"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="A2">
-            <v>1</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="A3">
-            <v>2</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="A4">
-            <v>3</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="A5">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="A6">
-            <v>5</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="A7">
-            <v>6</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="A8">
-            <v>7</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="A9">
-            <v>8</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="A10">
-            <v>9</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="A11">
-            <v>10</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="A12">
-            <v>11</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="A13">
-            <v>12</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="A14">
-            <v>13</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="A15">
-            <v>14</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="A16">
-            <v>15</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="A17">
-            <v>16</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="A18">
-            <v>17</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="A19">
-            <v>18</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="A20">
-            <v>19</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="A21">
-            <v>20</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="A22">
-            <v>21</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="A23">
-            <v>22</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="A24">
-            <v>23</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="A25">
-            <v>24</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="A26">
-            <v>25</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="A27">
-            <v>26</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="A28">
-            <v>27</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="A29">
-            <v>28</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="A30">
-            <v>29</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="A31">
-            <v>30</v>
-          </cell>
-        </row>
-        <row r="32">
-          <cell r="A32">
-            <v>31</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="A33">
-            <v>32</v>
-          </cell>
-        </row>
-        <row r="34">
-          <cell r="A34">
-            <v>33</v>
-          </cell>
-        </row>
-        <row r="35">
-          <cell r="A35">
-            <v>34</v>
-          </cell>
-        </row>
-        <row r="36">
-          <cell r="A36">
-            <v>35</v>
-          </cell>
-        </row>
-        <row r="37">
-          <cell r="A37">
-            <v>36</v>
-          </cell>
-        </row>
-        <row r="38">
-          <cell r="A38">
-            <v>37</v>
-          </cell>
-        </row>
-        <row r="39">
-          <cell r="A39">
-            <v>38</v>
-          </cell>
-        </row>
-        <row r="40">
-          <cell r="A40">
-            <v>39</v>
-          </cell>
-        </row>
-        <row r="41">
-          <cell r="A41">
-            <v>40</v>
-          </cell>
-        </row>
-        <row r="42">
-          <cell r="A42">
-            <v>41</v>
-          </cell>
-        </row>
-        <row r="43">
-          <cell r="A43">
-            <v>42</v>
-          </cell>
-        </row>
-        <row r="44">
-          <cell r="A44">
-            <v>43</v>
-          </cell>
-        </row>
-        <row r="45">
-          <cell r="A45">
-            <v>44</v>
-          </cell>
-        </row>
-        <row r="46">
-          <cell r="A46">
-            <v>45</v>
-          </cell>
-        </row>
-        <row r="47">
-          <cell r="A47">
-            <v>46</v>
-          </cell>
-        </row>
-        <row r="48">
-          <cell r="A48">
-            <v>47</v>
-          </cell>
-        </row>
-        <row r="49">
-          <cell r="A49">
-            <v>48</v>
-          </cell>
-        </row>
-        <row r="50">
-          <cell r="A50">
-            <v>49</v>
-          </cell>
-        </row>
-        <row r="51">
-          <cell r="A51">
-            <v>50</v>
-          </cell>
-        </row>
-        <row r="52">
-          <cell r="A52">
-            <v>51</v>
-          </cell>
-        </row>
-        <row r="53">
-          <cell r="A53">
-            <v>52</v>
-          </cell>
-        </row>
-        <row r="54">
-          <cell r="A54">
-            <v>53</v>
-          </cell>
-        </row>
-        <row r="55">
-          <cell r="A55">
-            <v>54</v>
-          </cell>
-        </row>
-        <row r="56">
-          <cell r="A56">
-            <v>55</v>
-          </cell>
-        </row>
-        <row r="57">
-          <cell r="A57">
-            <v>56</v>
-          </cell>
-        </row>
-        <row r="58">
-          <cell r="A58">
-            <v>57</v>
-          </cell>
-        </row>
-        <row r="59">
-          <cell r="A59">
-            <v>58</v>
-          </cell>
-        </row>
-        <row r="60">
-          <cell r="A60">
-            <v>59</v>
-          </cell>
-        </row>
-        <row r="61">
-          <cell r="A61">
-            <v>60</v>
-          </cell>
-        </row>
-        <row r="62">
-          <cell r="A62">
-            <v>61</v>
-          </cell>
-        </row>
-        <row r="63">
-          <cell r="A63">
-            <v>62</v>
-          </cell>
-        </row>
-        <row r="64">
-          <cell r="A64">
-            <v>63</v>
-          </cell>
-        </row>
-        <row r="65">
-          <cell r="A65">
-            <v>64</v>
-          </cell>
-        </row>
-        <row r="66">
-          <cell r="A66">
-            <v>65</v>
-          </cell>
-        </row>
-        <row r="67">
-          <cell r="A67">
-            <v>66</v>
-          </cell>
-        </row>
-        <row r="68">
-          <cell r="A68">
-            <v>67</v>
-          </cell>
-        </row>
-        <row r="69">
-          <cell r="A69">
-            <v>68</v>
-          </cell>
-        </row>
-        <row r="70">
-          <cell r="A70">
-            <v>69</v>
-          </cell>
-        </row>
-        <row r="71">
-          <cell r="A71">
-            <v>70</v>
-          </cell>
-        </row>
-        <row r="72">
-          <cell r="A72">
-            <v>71</v>
-          </cell>
-        </row>
-        <row r="73">
-          <cell r="A73">
-            <v>72</v>
-          </cell>
-        </row>
-        <row r="74">
-          <cell r="A74">
-            <v>73</v>
-          </cell>
-        </row>
-        <row r="75">
-          <cell r="A75">
-            <v>74</v>
-          </cell>
-        </row>
-        <row r="76">
-          <cell r="A76">
-            <v>75</v>
-          </cell>
-        </row>
-        <row r="77">
-          <cell r="A77">
-            <v>76</v>
-          </cell>
-        </row>
-        <row r="78">
-          <cell r="A78">
-            <v>77</v>
-          </cell>
-        </row>
-        <row r="79">
-          <cell r="A79">
-            <v>78</v>
-          </cell>
-        </row>
-        <row r="80">
-          <cell r="A80">
-            <v>79</v>
-          </cell>
-        </row>
-        <row r="81">
-          <cell r="A81">
-            <v>80</v>
-          </cell>
-        </row>
-        <row r="82">
-          <cell r="A82">
-            <v>81</v>
-          </cell>
-        </row>
-        <row r="83">
-          <cell r="A83">
-            <v>82</v>
-          </cell>
-        </row>
-        <row r="84">
-          <cell r="A84">
-            <v>83</v>
-          </cell>
-        </row>
-        <row r="85">
-          <cell r="A85">
-            <v>84</v>
-          </cell>
-        </row>
-        <row r="86">
-          <cell r="A86">
-            <v>85</v>
-          </cell>
-        </row>
-        <row r="87">
-          <cell r="A87">
-            <v>86</v>
-          </cell>
-        </row>
-        <row r="88">
-          <cell r="A88">
-            <v>87</v>
-          </cell>
-        </row>
-        <row r="89">
-          <cell r="A89">
-            <v>88</v>
-          </cell>
-        </row>
-        <row r="90">
-          <cell r="A90">
-            <v>89</v>
-          </cell>
-        </row>
-        <row r="91">
-          <cell r="A91">
-            <v>90</v>
-          </cell>
-        </row>
-        <row r="92">
-          <cell r="A92">
-            <v>91</v>
-          </cell>
-        </row>
-        <row r="93">
-          <cell r="A93">
-            <v>92</v>
-          </cell>
-        </row>
-        <row r="94">
-          <cell r="A94">
-            <v>93</v>
-          </cell>
-        </row>
-        <row r="95">
-          <cell r="A95">
-            <v>94</v>
-          </cell>
-        </row>
-        <row r="96">
-          <cell r="A96">
-            <v>95</v>
-          </cell>
-        </row>
-        <row r="97">
-          <cell r="A97">
-            <v>96</v>
-          </cell>
-        </row>
-        <row r="98">
-          <cell r="A98">
-            <v>97</v>
-          </cell>
-        </row>
-        <row r="99">
-          <cell r="A99">
-            <v>98</v>
-          </cell>
-        </row>
-        <row r="100">
-          <cell r="A100">
-            <v>99</v>
-          </cell>
-        </row>
-        <row r="101">
-          <cell r="A101">
-            <v>100</v>
-          </cell>
-        </row>
-        <row r="102">
-          <cell r="A102">
-            <v>101</v>
-          </cell>
-        </row>
-        <row r="103">
-          <cell r="A103">
-            <v>102</v>
-          </cell>
-        </row>
-        <row r="104">
-          <cell r="A104">
-            <v>103</v>
-          </cell>
-        </row>
-        <row r="105">
-          <cell r="A105">
-            <v>104</v>
-          </cell>
-        </row>
-        <row r="106">
-          <cell r="A106">
-            <v>105</v>
-          </cell>
-        </row>
-        <row r="107">
-          <cell r="A107">
-            <v>106</v>
-          </cell>
-        </row>
-        <row r="108">
-          <cell r="A108">
-            <v>107</v>
-          </cell>
-        </row>
-        <row r="109">
-          <cell r="A109">
-            <v>108</v>
-          </cell>
-        </row>
-        <row r="110">
-          <cell r="A110">
-            <v>109</v>
-          </cell>
-        </row>
-        <row r="111">
-          <cell r="A111">
-            <v>110</v>
-          </cell>
-        </row>
-        <row r="112">
-          <cell r="A112">
-            <v>111</v>
-          </cell>
-        </row>
-        <row r="113">
-          <cell r="A113">
-            <v>112</v>
-          </cell>
-        </row>
-        <row r="114">
-          <cell r="A114">
-            <v>113</v>
-          </cell>
-        </row>
-        <row r="115">
-          <cell r="A115">
-            <v>114</v>
-          </cell>
-        </row>
-        <row r="116">
-          <cell r="A116">
-            <v>115</v>
-          </cell>
-        </row>
-        <row r="117">
-          <cell r="A117">
-            <v>116</v>
-          </cell>
-        </row>
-        <row r="118">
-          <cell r="A118">
-            <v>117</v>
-          </cell>
-        </row>
-        <row r="119">
-          <cell r="A119">
-            <v>118</v>
-          </cell>
-        </row>
-        <row r="120">
-          <cell r="A120">
-            <v>119</v>
-          </cell>
-        </row>
-        <row r="121">
-          <cell r="A121">
-            <v>120</v>
-          </cell>
-        </row>
-        <row r="122">
-          <cell r="A122">
-            <v>121</v>
-          </cell>
-        </row>
-        <row r="123">
-          <cell r="A123">
-            <v>122</v>
-          </cell>
-        </row>
-        <row r="124">
-          <cell r="A124">
-            <v>123</v>
-          </cell>
-        </row>
-        <row r="125">
-          <cell r="A125">
-            <v>124</v>
-          </cell>
-        </row>
-        <row r="126">
-          <cell r="A126">
-            <v>125</v>
-          </cell>
-        </row>
-        <row r="127">
-          <cell r="A127">
-            <v>126</v>
-          </cell>
-        </row>
-        <row r="128">
-          <cell r="A128">
-            <v>127</v>
-          </cell>
-        </row>
-        <row r="129">
-          <cell r="A129">
-            <v>128</v>
-          </cell>
-        </row>
-        <row r="130">
-          <cell r="A130">
-            <v>129</v>
-          </cell>
-        </row>
-        <row r="131">
-          <cell r="A131">
-            <v>130</v>
-          </cell>
-        </row>
-        <row r="132">
-          <cell r="A132">
-            <v>131</v>
-          </cell>
-        </row>
-        <row r="133">
-          <cell r="A133">
-            <v>132</v>
-          </cell>
-        </row>
-        <row r="134">
-          <cell r="A134">
-            <v>133</v>
-          </cell>
-        </row>
-        <row r="135">
-          <cell r="A135">
-            <v>134</v>
-          </cell>
-        </row>
-        <row r="136">
-          <cell r="A136">
-            <v>135</v>
-          </cell>
-        </row>
-        <row r="137">
-          <cell r="A137">
-            <v>136</v>
-          </cell>
-        </row>
-        <row r="138">
-          <cell r="A138">
-            <v>137</v>
-          </cell>
-        </row>
-        <row r="139">
-          <cell r="A139">
-            <v>138</v>
-          </cell>
-        </row>
-        <row r="140">
-          <cell r="A140">
-            <v>139</v>
-          </cell>
-        </row>
-        <row r="141">
-          <cell r="A141">
-            <v>140</v>
-          </cell>
-        </row>
-        <row r="142">
-          <cell r="A142">
-            <v>141</v>
-          </cell>
-        </row>
-        <row r="143">
-          <cell r="A143">
-            <v>142</v>
-          </cell>
-        </row>
-        <row r="144">
-          <cell r="A144">
-            <v>143</v>
-          </cell>
-        </row>
-        <row r="145">
-          <cell r="A145">
-            <v>144</v>
-          </cell>
-        </row>
-        <row r="146">
-          <cell r="A146">
-            <v>145</v>
-          </cell>
-        </row>
-        <row r="147">
-          <cell r="A147">
-            <v>146</v>
-          </cell>
-        </row>
-        <row r="148">
-          <cell r="A148">
-            <v>147</v>
-          </cell>
-        </row>
-        <row r="149">
-          <cell r="A149">
-            <v>148</v>
-          </cell>
-        </row>
-        <row r="150">
-          <cell r="A150">
-            <v>149</v>
-          </cell>
-        </row>
-        <row r="151">
-          <cell r="A151">
-            <v>150</v>
-          </cell>
-        </row>
-        <row r="152">
-          <cell r="A152">
-            <v>151</v>
-          </cell>
-        </row>
-        <row r="153">
-          <cell r="A153">
-            <v>152</v>
-          </cell>
-        </row>
-        <row r="154">
-          <cell r="A154">
-            <v>153</v>
-          </cell>
-        </row>
-        <row r="155">
-          <cell r="A155">
-            <v>154</v>
-          </cell>
-        </row>
-        <row r="156">
-          <cell r="A156">
-            <v>155</v>
-          </cell>
-        </row>
-        <row r="157">
-          <cell r="A157">
-            <v>156</v>
-          </cell>
-        </row>
-        <row r="158">
-          <cell r="A158">
-            <v>157</v>
-          </cell>
-        </row>
-        <row r="159">
-          <cell r="A159">
-            <v>158</v>
-          </cell>
-        </row>
-        <row r="160">
-          <cell r="A160">
-            <v>159</v>
-          </cell>
-        </row>
-        <row r="161">
-          <cell r="A161">
-            <v>160</v>
-          </cell>
-        </row>
-        <row r="162">
-          <cell r="A162">
-            <v>161</v>
-          </cell>
-        </row>
-        <row r="163">
-          <cell r="A163">
-            <v>162</v>
-          </cell>
-        </row>
-        <row r="164">
-          <cell r="A164">
-            <v>163</v>
-          </cell>
-        </row>
-        <row r="165">
-          <cell r="A165">
-            <v>164</v>
-          </cell>
-        </row>
-        <row r="166">
-          <cell r="A166">
-            <v>165</v>
-          </cell>
-        </row>
-        <row r="167">
-          <cell r="A167">
-            <v>166</v>
-          </cell>
-        </row>
-        <row r="168">
-          <cell r="A168">
-            <v>167</v>
-          </cell>
-        </row>
-        <row r="169">
-          <cell r="A169">
-            <v>168</v>
-          </cell>
-        </row>
-        <row r="170">
-          <cell r="A170">
-            <v>169</v>
-          </cell>
-        </row>
-        <row r="171">
-          <cell r="A171">
-            <v>170</v>
-          </cell>
-        </row>
-        <row r="172">
-          <cell r="A172">
-            <v>171</v>
-          </cell>
-        </row>
-        <row r="173">
-          <cell r="A173">
-            <v>172</v>
-          </cell>
-        </row>
-        <row r="174">
-          <cell r="A174">
-            <v>173</v>
-          </cell>
-        </row>
-        <row r="175">
-          <cell r="A175">
-            <v>174</v>
-          </cell>
-        </row>
-        <row r="176">
-          <cell r="A176">
-            <v>175</v>
-          </cell>
-        </row>
-        <row r="177">
-          <cell r="A177">
-            <v>176</v>
-          </cell>
-        </row>
-        <row r="178">
-          <cell r="A178">
-            <v>177</v>
-          </cell>
-        </row>
-        <row r="179">
-          <cell r="A179">
-            <v>178</v>
-          </cell>
-        </row>
-        <row r="180">
-          <cell r="A180">
-            <v>179</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1">
-        <row r="2">
-          <cell r="A2">
-            <v>1000</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="A3">
-            <v>1001</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="A4">
-            <v>1002</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="A5">
-            <v>1003</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="A6">
-            <v>1004</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="A7">
-            <v>1005</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="A8">
-            <v>1006</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="A9">
-            <v>1007</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="A10">
-            <v>1008</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="A11">
-            <v>1009</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="A12">
-            <v>1010</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="A13">
-            <v>1011</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="A14">
-            <v>1012</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="A15">
-            <v>1013</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="A16">
-            <v>1014</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="A17">
-            <v>1015</v>
-          </cell>
-        </row>
-      </sheetData>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
       <sheetData sheetId="2">
         <row r="2">
           <cell r="A2">
@@ -2295,6 +1319,352 @@
           </cell>
         </row>
       </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="遥测"/>
+      <sheetName val="遥调"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="A2">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="A3">
+            <v>2</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="A4">
+            <v>3</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="A5">
+            <v>4</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="A6">
+            <v>5</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="A7">
+            <v>6</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="A8">
+            <v>7</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="A9">
+            <v>8</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="A10">
+            <v>9</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="A11">
+            <v>10</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="A12">
+            <v>11</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="A13">
+            <v>12</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="A14">
+            <v>13</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="A15">
+            <v>14</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="A16">
+            <v>15</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="A17">
+            <v>16</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="A18">
+            <v>17</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="A19">
+            <v>18</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="A20">
+            <v>19</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="A21">
+            <v>20</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="A22">
+            <v>21</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="A23">
+            <v>22</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="A24">
+            <v>23</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="A25">
+            <v>24</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="A26">
+            <v>25</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="A27">
+            <v>26</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="A28">
+            <v>27</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="A29">
+            <v>28</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="A30">
+            <v>29</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="A31">
+            <v>30</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="A32">
+            <v>31</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="A33">
+            <v>32</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="A34">
+            <v>33</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="A35">
+            <v>34</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="A36">
+            <v>35</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="A37">
+            <v>36</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="A38">
+            <v>40</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="A39">
+            <v>41</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="A40">
+            <v>42</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="A41">
+            <v>43</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="A42">
+            <v>44</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="A43">
+            <v>45</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="A44">
+            <v>46</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="A45">
+            <v>47</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="A46">
+            <v>48</v>
+          </cell>
+        </row>
+        <row r="47">
+          <cell r="A47">
+            <v>49</v>
+          </cell>
+        </row>
+        <row r="48">
+          <cell r="A48">
+            <v>50</v>
+          </cell>
+        </row>
+        <row r="49">
+          <cell r="A49">
+            <v>51</v>
+          </cell>
+        </row>
+        <row r="50">
+          <cell r="A50">
+            <v>52</v>
+          </cell>
+        </row>
+        <row r="51">
+          <cell r="A51">
+            <v>53</v>
+          </cell>
+        </row>
+        <row r="52">
+          <cell r="A52">
+            <v>54</v>
+          </cell>
+        </row>
+        <row r="53">
+          <cell r="A53">
+            <v>55</v>
+          </cell>
+        </row>
+        <row r="54">
+          <cell r="A54">
+            <v>56</v>
+          </cell>
+        </row>
+        <row r="55">
+          <cell r="A55">
+            <v>57</v>
+          </cell>
+        </row>
+        <row r="58">
+          <cell r="A58">
+            <v>60</v>
+          </cell>
+        </row>
+        <row r="59">
+          <cell r="A59">
+            <v>61</v>
+          </cell>
+        </row>
+        <row r="60">
+          <cell r="A60">
+            <v>62</v>
+          </cell>
+        </row>
+        <row r="61">
+          <cell r="A61">
+            <v>63</v>
+          </cell>
+        </row>
+        <row r="62">
+          <cell r="A62">
+            <v>64</v>
+          </cell>
+        </row>
+        <row r="63">
+          <cell r="A63">
+            <v>65</v>
+          </cell>
+        </row>
+        <row r="64">
+          <cell r="A64">
+            <v>66</v>
+          </cell>
+        </row>
+        <row r="65">
+          <cell r="A65">
+            <v>67</v>
+          </cell>
+        </row>
+        <row r="66">
+          <cell r="A66">
+            <v>68</v>
+          </cell>
+        </row>
+        <row r="67">
+          <cell r="A67">
+            <v>69</v>
+          </cell>
+        </row>
+        <row r="68">
+          <cell r="A68">
+            <v>70</v>
+          </cell>
+        </row>
+        <row r="69">
+          <cell r="A69">
+            <v>71</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3136,9 +2506,9 @@
   <dimension ref="A1:G6"/>
   <sheetFormatPr defaultColWidth="9.11111111111111" defaultRowHeight="18" outlineLevelRow="5" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="9.11111111111111" style="2"/>
+    <col min="1" max="1" width="11.7606837606838" style="2" customWidth="1"/>
     <col min="2" max="2" width="20.6752136752137" style="2" customWidth="1"/>
-    <col min="3" max="3" width="54.5470085470085" style="2" customWidth="1"/>
+    <col min="3" max="3" width="144.854700854701" style="2" customWidth="1"/>
     <col min="4" max="4" width="20.3931623931624" style="2" customWidth="1"/>
     <col min="5" max="5" width="10.2905982905983" style="2" customWidth="1"/>
     <col min="6" max="6" width="10.4358974358974" style="2" customWidth="1"/>
@@ -3170,8 +2540,8 @@
         <v>75</v>
       </c>
       <c r="C2" s="2" t="str">
-        <f>_xlfn.TEXTJOIN(",",TRUE,[1]遥信!$A$2:$A$1000)</f>
-        <v>1000,1001,1002,1003,1004,1005,1006,1007,1008,1009,1010,1011,1012,1013,1014,1015</v>
+        <f>_xlfn.TEXTJOIN(",",TRUE,[2]遥测!$A$58:$A$71)</f>
+        <v>60,61,62,63,64,65,66,67,68,69,70,71</v>
       </c>
       <c r="D2" s="2">
         <v>1</v>
@@ -3185,8 +2555,8 @@
         <v>76</v>
       </c>
       <c r="C3" s="2" t="str">
-        <f>_xlfn.TEXTJOIN(",",TRUE,[1]遥测!$A$2:$A$1000)</f>
-        <v>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23,24,25,26,27,28,29,30,31,32,33,34,35,36,37,38,39,40,41,42,43,44,45,46,47,48,49,50,51,52,53,54,55,56,57,58,59,60,61,62,63,64,65,66,67,68,69,70,71,72,73,74,75,76,77,78,79,80,81,82,83,84,85,86,87,88,89,90,91,92,93,94,95,96,97,98,99,100,101,102,103,104,105,106,107,108,109,110,111,112,113,114,115,116,117,118,119,120,121,122,123,124,125,126,127,128,129,130,131,132,133,134,135,136,137,138,139,140,141,142,143,144,145,146,147,148,149,150,151,152,153,154,155,156,157,158,159,160,161,162,163,164,165,166,167,168,169,170,171,172,173,174,175,176,177,178,179</v>
+        <f>_xlfn.TEXTJOIN(",",TRUE,[2]遥测!$A$2:$A$55)</f>
+        <v>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23,24,25,26,27,28,29,30,31,32,33,34,35,36,40,41,42,43,44,45,46,47,48,49,50,51,52,53,54,55,56,57</v>
       </c>
       <c r="D3" s="2">
         <v>1</v>

--- a/config/配置_v2.0.xlsx
+++ b/config/配置_v2.0.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="90">
   <si>
     <t>key</t>
   </si>
@@ -63,132 +63,159 @@
     <t>项目名称：</t>
   </si>
   <si>
+    <t>http_ip</t>
+  </si>
+  <si>
+    <t>0.0.0.0</t>
+  </si>
+  <si>
+    <t>HTTP监听IP</t>
+  </si>
+  <si>
+    <t>http_port</t>
+  </si>
+  <si>
+    <t>HTTP监听端口</t>
+  </si>
+  <si>
+    <t>mqtt_host</t>
+  </si>
+  <si>
+    <t>60.204.207.155</t>
+  </si>
+  <si>
+    <t>MQTT服务器地址</t>
+  </si>
+  <si>
+    <t>mqtt_port</t>
+  </si>
+  <si>
+    <t>MQTT服务器端口</t>
+  </si>
+  <si>
+    <t>mqtt_username</t>
+  </si>
+  <si>
+    <t>root</t>
+  </si>
+  <si>
+    <t>MQTT用户名</t>
+  </si>
+  <si>
+    <t>mqtt_password</t>
+  </si>
+  <si>
+    <t>inpower</t>
+  </si>
+  <si>
+    <t>MQTT密码</t>
+  </si>
+  <si>
+    <t>mqtt_yt</t>
+  </si>
+  <si>
+    <t>/asw/+/+/yt</t>
+  </si>
+  <si>
+    <t>MQTT遥调</t>
+  </si>
+  <si>
+    <t>mqtt_yk</t>
+  </si>
+  <si>
+    <t>/asw/+/+/yk</t>
+  </si>
+  <si>
+    <t>MQTT遥控</t>
+  </si>
+  <si>
+    <t>north_modbus_host</t>
+  </si>
+  <si>
+    <t>北向Modbus从机IP</t>
+  </si>
+  <si>
+    <t>north_modbus_port</t>
+  </si>
+  <si>
+    <t>北向Modbus从机端口</t>
+  </si>
+  <si>
+    <t>north_modbus_conf</t>
+  </si>
+  <si>
+    <t>./config/MODBUS_REGISTERS.xlsx</t>
+  </si>
+  <si>
+    <t>北向Modbus配置文件</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>desc</t>
+  </si>
+  <si>
+    <t>bcu1</t>
+  </si>
+  <si>
+    <t>BCU</t>
+  </si>
+  <si>
+    <t>pcs</t>
+  </si>
+  <si>
+    <t>PCS</t>
+  </si>
+  <si>
+    <t>liquidcool1</t>
+  </si>
+  <si>
+    <t>LiquidCool</t>
+  </si>
+  <si>
+    <t>liquidcool2</t>
+  </si>
+  <si>
+    <t>liquidcool3</t>
+  </si>
+  <si>
+    <t>firefighting</t>
+  </si>
+  <si>
+    <t>Firefighting</t>
+  </si>
+  <si>
+    <t>dehumidifier</t>
+  </si>
+  <si>
+    <t>Dehumidifier</t>
+  </si>
+  <si>
+    <t>comType</t>
+  </si>
+  <si>
+    <t>registerFile</t>
+  </si>
+  <si>
+    <t>interval</t>
+  </si>
+  <si>
+    <t>timeout</t>
+  </si>
+  <si>
     <t>ip</t>
   </si>
   <si>
-    <t>0.0.0.0</t>
-  </si>
-  <si>
-    <t>主机IP</t>
-  </si>
-  <si>
     <t>port</t>
   </si>
   <si>
-    <t>主机端口</t>
-  </si>
-  <si>
-    <t>mqtt_host</t>
-  </si>
-  <si>
-    <t>60.204.207.155</t>
-  </si>
-  <si>
-    <t>MQTT服务器地址</t>
-  </si>
-  <si>
-    <t>mqtt_port</t>
-  </si>
-  <si>
-    <t>MQTT服务器端口</t>
-  </si>
-  <si>
-    <t>mqtt_username</t>
-  </si>
-  <si>
-    <t>root</t>
-  </si>
-  <si>
-    <t>MQTT用户名</t>
-  </si>
-  <si>
-    <t>mqtt_password</t>
-  </si>
-  <si>
-    <t>inpower</t>
-  </si>
-  <si>
-    <t>MQTT密码</t>
-  </si>
-  <si>
-    <t>mqtt_yt</t>
-  </si>
-  <si>
-    <t>/asw/+/+/yt</t>
-  </si>
-  <si>
-    <t>MQTT遥调</t>
-  </si>
-  <si>
-    <t>mqtt_yk</t>
-  </si>
-  <si>
-    <t>/asw/+/+/yk</t>
-  </si>
-  <si>
-    <t>MQTT遥控</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>type</t>
-  </si>
-  <si>
-    <t>desc</t>
-  </si>
-  <si>
-    <t>bcu1</t>
-  </si>
-  <si>
-    <t>BCU</t>
-  </si>
-  <si>
-    <t>pcs</t>
-  </si>
-  <si>
-    <t>PCS</t>
-  </si>
-  <si>
-    <t>liquidcool1</t>
-  </si>
-  <si>
-    <t>LiquidCool</t>
-  </si>
-  <si>
-    <t>liquidcool2</t>
-  </si>
-  <si>
-    <t>liquidcool3</t>
-  </si>
-  <si>
-    <t>firefighting</t>
-  </si>
-  <si>
-    <t>Firefighting</t>
-  </si>
-  <si>
-    <t>dehumidifier</t>
-  </si>
-  <si>
-    <t>Dehumidifier</t>
-  </si>
-  <si>
-    <t>comType</t>
-  </si>
-  <si>
-    <t>registerFile</t>
-  </si>
-  <si>
-    <t>interval</t>
-  </si>
-  <si>
-    <t>timeout</t>
-  </si>
-  <si>
     <t>slave</t>
   </si>
   <si>
@@ -222,7 +249,7 @@
     <t>ModbusTCP</t>
   </si>
   <si>
-    <t>./config/PCS_英博_大机.xlsx</t>
+    <t>./config/PCS_125_英博.xlsx</t>
   </si>
   <si>
     <t>127.0.0.1</t>
@@ -1920,10 +1947,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr defaultColWidth="22.4017094017094" defaultRowHeight="18" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="16384" width="22.4017094017094" style="3"/>
+    <col min="1" max="1" width="22.4017094017094" style="3"/>
+    <col min="2" max="2" width="33.7948717948718" style="3" customWidth="1"/>
+    <col min="3" max="16384" width="22.4017094017094" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2045,6 +2074,39 @@
       </c>
       <c r="C11" s="3" t="s">
         <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="3">
+        <v>9092</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -2068,16 +2130,16 @@
   <sheetData>
     <row r="1" s="4" customFormat="1" spans="1:5">
       <c r="A1" s="4" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="E1" s="3"/>
     </row>
@@ -2086,10 +2148,10 @@
         <v>0</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -2097,10 +2159,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -2108,10 +2170,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -2119,10 +2181,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -2130,10 +2192,10 @@
         <v>4</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -2141,10 +2203,10 @@
         <v>5</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -2152,10 +2214,10 @@
         <v>6</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -2184,55 +2246,55 @@
   <sheetData>
     <row r="1" s="4" customFormat="1" spans="1:17">
       <c r="A1" s="4" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>9</v>
+        <v>58</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>12</v>
+        <v>59</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="O1" s="5" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="P1" s="5" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="Q1" s="4" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:17">
@@ -2241,16 +2303,16 @@
         <v>0</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="F2" s="3">
         <v>1000</v>
@@ -2262,7 +2324,7 @@
         <v>500000</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:17">
@@ -2271,16 +2333,16 @@
         <v>1</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="F3" s="3">
         <v>1000</v>
@@ -2289,7 +2351,7 @@
         <v>500</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="I3" s="3">
         <v>33434</v>
@@ -2304,13 +2366,13 @@
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="F4" s="3">
         <v>1000</v>
@@ -2322,7 +2384,7 @@
         <v>1</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="L4" s="3">
         <v>9600</v>
@@ -2331,7 +2393,7 @@
         <v>8</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="O4" s="3">
         <v>1</v>
@@ -2343,13 +2405,13 @@
         <v>3</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="F5" s="3">
         <v>1000</v>
@@ -2361,7 +2423,7 @@
         <v>1</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="L5" s="3">
         <v>9600</v>
@@ -2370,7 +2432,7 @@
         <v>8</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="O5" s="3">
         <v>1</v>
@@ -2382,13 +2444,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="F6" s="3">
         <v>1000</v>
@@ -2400,7 +2462,7 @@
         <v>1</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="L6" s="3">
         <v>9600</v>
@@ -2409,7 +2471,7 @@
         <v>8</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="O6" s="3">
         <v>1</v>
@@ -2421,13 +2483,13 @@
         <v>5</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="F7" s="3">
         <v>1000</v>
@@ -2439,7 +2501,7 @@
         <v>1</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="L7" s="3">
         <v>9600</v>
@@ -2448,7 +2510,7 @@
         <v>8</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="O7" s="3">
         <v>1</v>
@@ -2460,13 +2522,13 @@
         <v>6</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="F8" s="3">
         <v>1000</v>
@@ -2478,7 +2540,7 @@
         <v>1</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="L8" s="3">
         <v>9600</v>
@@ -2487,7 +2549,7 @@
         <v>8</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="O8" s="3">
         <v>1</v>
@@ -2517,16 +2579,16 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
@@ -2534,10 +2596,10 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="2" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="C2" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[2]遥测!$A$58:$A$71)</f>
@@ -2549,10 +2611,10 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="2" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="C3" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[2]遥测!$A$2:$A$55)</f>
@@ -2564,10 +2626,10 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="2" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="C4" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[1]遥调!$A$2:$A$1000)</f>
@@ -2579,10 +2641,10 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="2" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C5" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[1]遥控!$A$2:$A$1000)</f>
@@ -2594,13 +2656,13 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="2" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="D6" s="2">
         <v>1</v>

--- a/config/配置_v2.0.xlsx
+++ b/config/配置_v2.0.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="22010" windowHeight="12332"/>
+    <workbookView windowWidth="18519" windowHeight="11218"/>
   </bookViews>
   <sheets>
     <sheet name="project" sheetId="1" r:id="rId1"/>

--- a/config/配置_v2.0.xlsx
+++ b/config/配置_v2.0.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="18519" windowHeight="11218"/>
+    <workbookView windowWidth="18569" windowHeight="10825" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="project" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="83">
   <si>
     <t>key</t>
   </si>
@@ -253,27 +253,6 @@
   </si>
   <si>
     <t>127.0.0.1</t>
-  </si>
-  <si>
-    <t>ModbusRTU</t>
-  </si>
-  <si>
-    <t>/dev/ttyXRUSB2</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>/dev/ttyXRUSB3</t>
-  </si>
-  <si>
-    <t>/dev/ttyXRUSB1</t>
-  </si>
-  <si>
-    <t>/dev/ttyXRUSB4</t>
-  </si>
-  <si>
-    <t>/dev/ttyXRUSB5</t>
   </si>
   <si>
     <t>device_id</t>
@@ -1948,11 +1927,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="22.4017094017094" defaultRowHeight="18" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="22.4047619047619" defaultRowHeight="18" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="22.4017094017094" style="3"/>
-    <col min="2" max="2" width="33.7948717948718" style="3" customWidth="1"/>
-    <col min="3" max="16384" width="22.4017094017094" style="3"/>
+    <col min="1" max="1" width="22.4047619047619" style="3"/>
+    <col min="2" max="2" width="33.7936507936508" style="3" customWidth="1"/>
+    <col min="3" max="16384" width="22.4047619047619" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2122,8 +2101,8 @@
   <dimension ref="A1:E8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelRow="7" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="6.46153846153846" style="3" customWidth="1"/>
-    <col min="2" max="2" width="20.9316239316239" style="3" customWidth="1"/>
+    <col min="1" max="1" width="6.46031746031746" style="3" customWidth="1"/>
+    <col min="2" max="2" width="20.9285714285714" style="3" customWidth="1"/>
     <col min="3" max="3" width="20.3333333333333" style="3" customWidth="1"/>
     <col min="4" max="16384" width="9" style="3"/>
   </cols>
@@ -2230,18 +2209,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:Q8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelRow="7"/>
+  <dimension ref="A1:Q3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelRow="2"/>
   <cols>
-    <col min="1" max="1" width="6.46153846153846" style="3" customWidth="1"/>
-    <col min="2" max="2" width="15.5982905982906" style="3" customWidth="1"/>
-    <col min="3" max="3" width="13.4615384615385" style="3" customWidth="1"/>
-    <col min="4" max="4" width="12.9316239316239" style="3" customWidth="1"/>
-    <col min="5" max="5" width="44.5299145299145" style="3" customWidth="1"/>
-    <col min="6" max="10" width="12.1965811965812" style="3" customWidth="1"/>
+    <col min="1" max="1" width="6.46031746031746" style="3" customWidth="1"/>
+    <col min="2" max="2" width="15.5952380952381" style="3" customWidth="1"/>
+    <col min="3" max="3" width="13.4603174603175" style="3" customWidth="1"/>
+    <col min="4" max="4" width="12.9285714285714" style="3" customWidth="1"/>
+    <col min="5" max="5" width="44.531746031746" style="3" customWidth="1"/>
+    <col min="6" max="10" width="12.1984126984127" style="3" customWidth="1"/>
     <col min="11" max="11" width="16.6666666666667" style="3" customWidth="1"/>
-    <col min="12" max="16" width="12.1965811965812" style="3" customWidth="1"/>
-    <col min="17" max="16384" width="9.06837606837607" style="3"/>
+    <col min="12" max="16" width="12.1984126984127" style="3" customWidth="1"/>
+    <col min="17" max="16384" width="9.07142857142857" style="3"/>
   </cols>
   <sheetData>
     <row r="1" s="4" customFormat="1" spans="1:17">
@@ -2318,7 +2297,7 @@
         <v>1000</v>
       </c>
       <c r="G2" s="3">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="L2" s="3">
         <v>500000</v>
@@ -2345,10 +2324,10 @@
         <v>71</v>
       </c>
       <c r="F3" s="3">
+        <v>2000</v>
+      </c>
+      <c r="G3" s="3">
         <v>1000</v>
-      </c>
-      <c r="G3" s="3">
-        <v>500</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>72</v>
@@ -2357,201 +2336,6 @@
         <v>33434</v>
       </c>
       <c r="J3" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17">
-      <c r="A4" s="3">
-        <f>devices!A4</f>
-        <v>2</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F4" s="3">
-        <v>1000</v>
-      </c>
-      <c r="G4" s="3">
-        <v>500</v>
-      </c>
-      <c r="J4" s="3">
-        <v>1</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="L4" s="3">
-        <v>9600</v>
-      </c>
-      <c r="M4" s="3">
-        <v>8</v>
-      </c>
-      <c r="N4" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="O4" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17">
-      <c r="A5" s="3">
-        <f>devices!A5</f>
-        <v>3</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F5" s="3">
-        <v>1000</v>
-      </c>
-      <c r="G5" s="3">
-        <v>500</v>
-      </c>
-      <c r="J5" s="3">
-        <v>1</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="L5" s="3">
-        <v>9600</v>
-      </c>
-      <c r="M5" s="3">
-        <v>8</v>
-      </c>
-      <c r="N5" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="O5" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17">
-      <c r="A6" s="3">
-        <f>devices!A6</f>
-        <v>4</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F6" s="3">
-        <v>1000</v>
-      </c>
-      <c r="G6" s="3">
-        <v>500</v>
-      </c>
-      <c r="J6" s="3">
-        <v>1</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="L6" s="3">
-        <v>9600</v>
-      </c>
-      <c r="M6" s="3">
-        <v>8</v>
-      </c>
-      <c r="N6" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="O6" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17">
-      <c r="A7" s="3">
-        <f>devices!A7</f>
-        <v>5</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F7" s="3">
-        <v>1000</v>
-      </c>
-      <c r="G7" s="3">
-        <v>500</v>
-      </c>
-      <c r="J7" s="3">
-        <v>1</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="L7" s="3">
-        <v>9600</v>
-      </c>
-      <c r="M7" s="3">
-        <v>8</v>
-      </c>
-      <c r="N7" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="O7" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17">
-      <c r="A8" s="3">
-        <f>devices!A8</f>
-        <v>6</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F8" s="3">
-        <v>1000</v>
-      </c>
-      <c r="G8" s="3">
-        <v>500</v>
-      </c>
-      <c r="J8" s="3">
-        <v>1</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="L8" s="3">
-        <v>9600</v>
-      </c>
-      <c r="M8" s="3">
-        <v>8</v>
-      </c>
-      <c r="N8" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="O8" s="3">
         <v>1</v>
       </c>
     </row>
@@ -2568,27 +2352,27 @@
   <dimension ref="A1:G6"/>
   <sheetFormatPr defaultColWidth="9.11111111111111" defaultRowHeight="18" outlineLevelRow="5" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="11.7606837606838" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.6752136752137" style="2" customWidth="1"/>
-    <col min="3" max="3" width="144.854700854701" style="2" customWidth="1"/>
-    <col min="4" max="4" width="20.3931623931624" style="2" customWidth="1"/>
-    <col min="5" max="5" width="10.2905982905983" style="2" customWidth="1"/>
-    <col min="6" max="6" width="10.4358974358974" style="2" customWidth="1"/>
+    <col min="1" max="1" width="11.7619047619048" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.6746031746032" style="2" customWidth="1"/>
+    <col min="3" max="3" width="144.857142857143" style="2" customWidth="1"/>
+    <col min="4" max="4" width="20.3968253968254" style="2" customWidth="1"/>
+    <col min="5" max="5" width="10.2936507936508" style="2" customWidth="1"/>
+    <col min="6" max="6" width="10.4365079365079" style="2" customWidth="1"/>
     <col min="7" max="16384" width="9.11111111111111" style="2"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
@@ -2599,7 +2383,7 @@
         <v>44</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="C2" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[2]遥测!$A$58:$A$71)</f>
@@ -2614,7 +2398,7 @@
         <v>44</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="C3" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[2]遥测!$A$2:$A$55)</f>
@@ -2629,7 +2413,7 @@
         <v>44</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="C4" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[1]遥调!$A$2:$A$1000)</f>
@@ -2644,7 +2428,7 @@
         <v>44</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="C5" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[1]遥控!$A$2:$A$1000)</f>
@@ -2659,10 +2443,10 @@
         <v>42</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="D6" s="2">
         <v>1</v>

--- a/config/配置_v2.0.xlsx
+++ b/config/配置_v2.0.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="18569" windowHeight="10825" activeTab="2"/>
+    <workbookView windowWidth="18519" windowHeight="10774"/>
   </bookViews>
   <sheets>
     <sheet name="project" sheetId="1" r:id="rId1"/>

--- a/config/配置_v2.0.xlsx
+++ b/config/配置_v2.0.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="18519" windowHeight="10774"/>
+    <workbookView windowWidth="18569" windowHeight="11268" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="project" sheetId="1" r:id="rId1"/>
@@ -12,10 +12,6 @@
     <sheet name="config" sheetId="4" r:id="rId3"/>
     <sheet name="mqtt_routes" sheetId="5" r:id="rId4"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId5"/>
-    <externalReference r:id="rId6"/>
-  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -34,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="90">
   <si>
     <t>key</t>
   </si>
@@ -57,7 +53,7 @@
     <t>project</t>
   </si>
   <si>
-    <t>康明斯</t>
+    <t>英博自研</t>
   </si>
   <si>
     <t>项目名称：</t>
@@ -81,7 +77,7 @@
     <t>mqtt_host</t>
   </si>
   <si>
-    <t>60.204.207.155</t>
+    <t>127.0.0.1</t>
   </si>
   <si>
     <t>MQTT服务器地址</t>
@@ -162,40 +158,49 @@
     <t>desc</t>
   </si>
   <si>
-    <t>bcu1</t>
+    <t>pcs</t>
+  </si>
+  <si>
+    <t>PCS</t>
+  </si>
+  <si>
+    <t>英博电气125kWPCS</t>
+  </si>
+  <si>
+    <t>bcu</t>
   </si>
   <si>
     <t>BCU</t>
   </si>
   <si>
-    <t>pcs</t>
-  </si>
-  <si>
-    <t>PCS</t>
-  </si>
-  <si>
-    <t>liquidcool1</t>
-  </si>
-  <si>
-    <t>LiquidCool</t>
-  </si>
-  <si>
-    <t>liquidcool2</t>
-  </si>
-  <si>
-    <t>liquidcool3</t>
-  </si>
-  <si>
-    <t>firefighting</t>
-  </si>
-  <si>
-    <t>Firefighting</t>
-  </si>
-  <si>
-    <t>dehumidifier</t>
-  </si>
-  <si>
-    <t>Dehumidifier</t>
+    <t>永泰BMS系统</t>
+  </si>
+  <si>
+    <t>dehum</t>
+  </si>
+  <si>
+    <t>Dehum</t>
+  </si>
+  <si>
+    <t>除湿机</t>
+  </si>
+  <si>
+    <t>tms</t>
+  </si>
+  <si>
+    <t>TMS</t>
+  </si>
+  <si>
+    <t>液冷机组</t>
+  </si>
+  <si>
+    <t>fire</t>
+  </si>
+  <si>
+    <t>FIRE</t>
+  </si>
+  <si>
+    <t>消防系统</t>
   </si>
   <si>
     <t>comType</t>
@@ -237,22 +242,52 @@
     <t>interface</t>
   </si>
   <si>
+    <t>requestInterval</t>
+  </si>
+  <si>
+    <t>maxGap</t>
+  </si>
+  <si>
+    <t>ModbusTCP</t>
+  </si>
+  <si>
+    <t>./config/PCS_125_英博.xlsx</t>
+  </si>
+  <si>
+    <t>192.168.0.20</t>
+  </si>
+  <si>
     <t>CAN</t>
   </si>
   <si>
-    <t>./config/BCU_GOLD.xlsx</t>
-  </si>
-  <si>
-    <t>vcan0</t>
-  </si>
-  <si>
-    <t>ModbusTCP</t>
-  </si>
-  <si>
-    <t>./config/PCS_125_英博.xlsx</t>
-  </si>
-  <si>
-    <t>127.0.0.1</t>
+    <t>./config/永泰_2_BCU.xlsx</t>
+  </si>
+  <si>
+    <t>can0</t>
+  </si>
+  <si>
+    <t>ModbusRTU</t>
+  </si>
+  <si>
+    <t>./config/除湿机.xlsx</t>
+  </si>
+  <si>
+    <t>/dev/ttyXRUSB1</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>./config/水冷机组_埃森特.xlsx</t>
+  </si>
+  <si>
+    <t>/dev/ttyXRUSB3</t>
+  </si>
+  <si>
+    <t>./config/消防温感烟感.xlsx</t>
+  </si>
+  <si>
+    <t>/dev/ttyXRUSB2</t>
   </si>
   <si>
     <t>device_id</t>
@@ -265,24 +300,6 @@
   </si>
   <si>
     <t>enable</t>
-  </si>
-  <si>
-    <t>/pcs/0/yx</t>
-  </si>
-  <si>
-    <t>/pcs/0/yc</t>
-  </si>
-  <si>
-    <t>/pcs/0/yt</t>
-  </si>
-  <si>
-    <t>/pcs/0/yk</t>
-  </si>
-  <si>
-    <t>/bcu/0/yc</t>
-  </si>
-  <si>
-    <t>1,2,2001</t>
   </si>
 </sst>
 </file>
@@ -295,7 +312,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -312,15 +329,21 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -804,137 +827,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -950,7 +973,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1012,668 +1038,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="遥测"/>
-      <sheetName val="遥信"/>
-      <sheetName val="遥调"/>
-      <sheetName val="遥控"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2">
-        <row r="2">
-          <cell r="A2">
-            <v>2000</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="A3">
-            <v>2001</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="A4">
-            <v>2002</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="A5">
-            <v>2003</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="A6">
-            <v>2004</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="A7">
-            <v>2005</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="A8">
-            <v>2006</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="A9">
-            <v>2007</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="A10">
-            <v>2008</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="A11">
-            <v>2009</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="A12">
-            <v>2010</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="A13">
-            <v>2011</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="A14">
-            <v>2012</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="A15">
-            <v>2013</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="A16">
-            <v>2014</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="A17">
-            <v>2015</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="A18">
-            <v>2016</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="A19">
-            <v>2017</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="A20">
-            <v>2018</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="A21">
-            <v>2019</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="A22">
-            <v>2020</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="A23">
-            <v>2021</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="A24">
-            <v>2022</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="A25">
-            <v>2023</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="A26">
-            <v>2024</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="A27">
-            <v>2025</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="A28">
-            <v>2026</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="A29">
-            <v>2027</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="A30">
-            <v>2028</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="A31">
-            <v>2029</v>
-          </cell>
-        </row>
-        <row r="32">
-          <cell r="A32">
-            <v>2030</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="A33">
-            <v>2031</v>
-          </cell>
-        </row>
-        <row r="34">
-          <cell r="A34">
-            <v>2032</v>
-          </cell>
-        </row>
-        <row r="35">
-          <cell r="A35">
-            <v>2033</v>
-          </cell>
-        </row>
-        <row r="36">
-          <cell r="A36">
-            <v>2034</v>
-          </cell>
-        </row>
-        <row r="37">
-          <cell r="A37">
-            <v>2035</v>
-          </cell>
-        </row>
-        <row r="38">
-          <cell r="A38">
-            <v>2036</v>
-          </cell>
-        </row>
-        <row r="39">
-          <cell r="A39">
-            <v>2037</v>
-          </cell>
-        </row>
-        <row r="40">
-          <cell r="A40">
-            <v>2038</v>
-          </cell>
-        </row>
-        <row r="41">
-          <cell r="A41">
-            <v>2039</v>
-          </cell>
-        </row>
-        <row r="42">
-          <cell r="A42">
-            <v>2040</v>
-          </cell>
-        </row>
-        <row r="43">
-          <cell r="A43">
-            <v>2041</v>
-          </cell>
-        </row>
-        <row r="44">
-          <cell r="A44">
-            <v>2042</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="3">
-        <row r="2">
-          <cell r="A2">
-            <v>3000</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="A3">
-            <v>3001</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="A4">
-            <v>3002</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="A5">
-            <v>3003</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="A6">
-            <v>3004</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="A7">
-            <v>3005</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="A8">
-            <v>3006</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="A9">
-            <v>3007</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="A10">
-            <v>3008</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="A11">
-            <v>3009</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="A12">
-            <v>3010</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="A13">
-            <v>3011</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="A14">
-            <v>3012</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="A15">
-            <v>3013</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="A16">
-            <v>3014</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="A17">
-            <v>3015</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="遥测"/>
-      <sheetName val="遥调"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="A2">
-            <v>1</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="A3">
-            <v>2</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="A4">
-            <v>3</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="A5">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="A6">
-            <v>5</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="A7">
-            <v>6</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="A8">
-            <v>7</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="A9">
-            <v>8</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="A10">
-            <v>9</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="A11">
-            <v>10</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="A12">
-            <v>11</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="A13">
-            <v>12</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="A14">
-            <v>13</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="A15">
-            <v>14</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="A16">
-            <v>15</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="A17">
-            <v>16</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="A18">
-            <v>17</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="A19">
-            <v>18</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="A20">
-            <v>19</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="A21">
-            <v>20</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="A22">
-            <v>21</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="A23">
-            <v>22</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="A24">
-            <v>23</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="A25">
-            <v>24</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="A26">
-            <v>25</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="A27">
-            <v>26</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="A28">
-            <v>27</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="A29">
-            <v>28</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="A30">
-            <v>29</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="A31">
-            <v>30</v>
-          </cell>
-        </row>
-        <row r="32">
-          <cell r="A32">
-            <v>31</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="A33">
-            <v>32</v>
-          </cell>
-        </row>
-        <row r="34">
-          <cell r="A34">
-            <v>33</v>
-          </cell>
-        </row>
-        <row r="35">
-          <cell r="A35">
-            <v>34</v>
-          </cell>
-        </row>
-        <row r="36">
-          <cell r="A36">
-            <v>35</v>
-          </cell>
-        </row>
-        <row r="37">
-          <cell r="A37">
-            <v>36</v>
-          </cell>
-        </row>
-        <row r="38">
-          <cell r="A38">
-            <v>40</v>
-          </cell>
-        </row>
-        <row r="39">
-          <cell r="A39">
-            <v>41</v>
-          </cell>
-        </row>
-        <row r="40">
-          <cell r="A40">
-            <v>42</v>
-          </cell>
-        </row>
-        <row r="41">
-          <cell r="A41">
-            <v>43</v>
-          </cell>
-        </row>
-        <row r="42">
-          <cell r="A42">
-            <v>44</v>
-          </cell>
-        </row>
-        <row r="43">
-          <cell r="A43">
-            <v>45</v>
-          </cell>
-        </row>
-        <row r="44">
-          <cell r="A44">
-            <v>46</v>
-          </cell>
-        </row>
-        <row r="45">
-          <cell r="A45">
-            <v>47</v>
-          </cell>
-        </row>
-        <row r="46">
-          <cell r="A46">
-            <v>48</v>
-          </cell>
-        </row>
-        <row r="47">
-          <cell r="A47">
-            <v>49</v>
-          </cell>
-        </row>
-        <row r="48">
-          <cell r="A48">
-            <v>50</v>
-          </cell>
-        </row>
-        <row r="49">
-          <cell r="A49">
-            <v>51</v>
-          </cell>
-        </row>
-        <row r="50">
-          <cell r="A50">
-            <v>52</v>
-          </cell>
-        </row>
-        <row r="51">
-          <cell r="A51">
-            <v>53</v>
-          </cell>
-        </row>
-        <row r="52">
-          <cell r="A52">
-            <v>54</v>
-          </cell>
-        </row>
-        <row r="53">
-          <cell r="A53">
-            <v>55</v>
-          </cell>
-        </row>
-        <row r="54">
-          <cell r="A54">
-            <v>56</v>
-          </cell>
-        </row>
-        <row r="55">
-          <cell r="A55">
-            <v>57</v>
-          </cell>
-        </row>
-        <row r="58">
-          <cell r="A58">
-            <v>60</v>
-          </cell>
-        </row>
-        <row r="59">
-          <cell r="A59">
-            <v>61</v>
-          </cell>
-        </row>
-        <row r="60">
-          <cell r="A60">
-            <v>62</v>
-          </cell>
-        </row>
-        <row r="61">
-          <cell r="A61">
-            <v>63</v>
-          </cell>
-        </row>
-        <row r="62">
-          <cell r="A62">
-            <v>64</v>
-          </cell>
-        </row>
-        <row r="63">
-          <cell r="A63">
-            <v>65</v>
-          </cell>
-        </row>
-        <row r="64">
-          <cell r="A64">
-            <v>66</v>
-          </cell>
-        </row>
-        <row r="65">
-          <cell r="A65">
-            <v>67</v>
-          </cell>
-        </row>
-        <row r="66">
-          <cell r="A66">
-            <v>68</v>
-          </cell>
-        </row>
-        <row r="67">
-          <cell r="A67">
-            <v>69</v>
-          </cell>
-        </row>
-        <row r="68">
-          <cell r="A68">
-            <v>70</v>
-          </cell>
-        </row>
-        <row r="69">
-          <cell r="A69">
-            <v>71</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1929,162 +1293,162 @@
   <dimension ref="A1:C14"/>
   <sheetFormatPr defaultColWidth="22.4047619047619" defaultRowHeight="18" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="22.4047619047619" style="3"/>
-    <col min="2" max="2" width="33.7936507936508" style="3" customWidth="1"/>
-    <col min="3" max="16384" width="22.4047619047619" style="3"/>
+    <col min="1" max="1" width="22.4047619047619" style="4"/>
+    <col min="2" max="2" width="33.7936507936508" style="4" customWidth="1"/>
+    <col min="3" max="16384" width="22.4047619047619" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="4">
         <v>9091</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="3">
-        <v>9131</v>
-      </c>
-      <c r="C7" s="3" t="s">
+      <c r="B7" s="4">
+        <v>1883</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="4" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="4" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="4" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="4" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="4" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B13" s="3">
+      <c r="B13" s="4">
         <v>9092</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="4" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="4" t="s">
         <v>37</v>
       </c>
     </row>
@@ -2098,105 +1462,99 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelRow="7" outlineLevelCol="4"/>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelRow="5" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="6.46031746031746" style="3" customWidth="1"/>
-    <col min="2" max="2" width="20.9285714285714" style="3" customWidth="1"/>
-    <col min="3" max="3" width="20.3333333333333" style="3" customWidth="1"/>
-    <col min="4" max="16384" width="9" style="3"/>
+    <col min="1" max="1" width="6.46031746031746" style="4" customWidth="1"/>
+    <col min="2" max="2" width="20.9285714285714" style="4" customWidth="1"/>
+    <col min="3" max="3" width="20.3333333333333" style="4" customWidth="1"/>
+    <col min="4" max="4" width="17.5396825396825" style="4" customWidth="1"/>
+    <col min="5" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" s="4" customFormat="1" spans="1:5">
-      <c r="A1" s="4" t="s">
+    <row r="1" s="3" customFormat="1" spans="1:5">
+      <c r="A1" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E1" s="3"/>
+      <c r="E1" s="4"/>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="3">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
+      <c r="A2" s="4">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>43</v>
       </c>
+      <c r="D2" s="4" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="3">
-        <v>1</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C3" s="3" t="s">
+      <c r="A3" s="4">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>45</v>
       </c>
+      <c r="C3" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="3">
-        <v>2</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>47</v>
+      <c r="A4" s="4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="3">
-        <v>3</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>47</v>
+      <c r="A5" s="4">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="3">
-        <v>4</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="3">
+      <c r="A6" s="4">
         <v>5</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="3">
-        <v>6</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>53</v>
+      <c r="B6" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -2209,133 +1567,265 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:Q3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelRow="2"/>
+  <dimension ref="A1:S6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelRow="5"/>
   <cols>
-    <col min="1" max="1" width="6.46031746031746" style="3" customWidth="1"/>
-    <col min="2" max="2" width="15.5952380952381" style="3" customWidth="1"/>
-    <col min="3" max="3" width="13.4603174603175" style="3" customWidth="1"/>
-    <col min="4" max="4" width="12.9285714285714" style="3" customWidth="1"/>
-    <col min="5" max="5" width="44.531746031746" style="3" customWidth="1"/>
-    <col min="6" max="10" width="12.1984126984127" style="3" customWidth="1"/>
-    <col min="11" max="11" width="16.6666666666667" style="3" customWidth="1"/>
-    <col min="12" max="16" width="12.1984126984127" style="3" customWidth="1"/>
-    <col min="17" max="16384" width="9.07142857142857" style="3"/>
+    <col min="1" max="1" width="6.46031746031746" style="4" customWidth="1"/>
+    <col min="2" max="2" width="15.5952380952381" style="4" customWidth="1"/>
+    <col min="3" max="3" width="13.4603174603175" style="4" customWidth="1"/>
+    <col min="4" max="4" width="12.9285714285714" style="4" customWidth="1"/>
+    <col min="5" max="5" width="44.531746031746" style="4" customWidth="1"/>
+    <col min="6" max="10" width="12.1984126984127" style="4" customWidth="1"/>
+    <col min="11" max="11" width="16.6666666666667" style="4" customWidth="1"/>
+    <col min="12" max="16" width="12.1984126984127" style="4" customWidth="1"/>
+    <col min="17" max="17" width="9.07142857142857" style="4"/>
+    <col min="18" max="18" width="15.2142857142857" style="4" customWidth="1"/>
+    <col min="19" max="16384" width="9.07142857142857" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" s="4" customFormat="1" spans="1:17">
-      <c r="A1" s="4" t="s">
+    <row r="1" s="3" customFormat="1" spans="1:19">
+      <c r="A1" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N1" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="P1" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="R1" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="S1" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19">
+      <c r="A2" s="4">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F2" s="4">
+        <v>2000</v>
+      </c>
+      <c r="G2" s="4">
+        <v>2000</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="I2" s="4">
+        <v>502</v>
+      </c>
+      <c r="J2" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19">
+      <c r="A3" s="4">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F3" s="4">
+        <v>2000</v>
+      </c>
+      <c r="G3" s="4">
+        <v>2000</v>
+      </c>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="L3" s="4">
+        <v>500000</v>
+      </c>
+      <c r="P3" s="4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19">
+      <c r="A4" s="4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F4" s="4">
+        <v>2000</v>
+      </c>
+      <c r="G4" s="4">
+        <v>2000</v>
+      </c>
+      <c r="J4" s="4">
+        <v>2</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="L4" s="4">
+        <v>9600</v>
+      </c>
+      <c r="M4" s="4">
+        <v>8</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="O4" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19">
+      <c r="A5" s="4">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="F5" s="4">
+        <v>2000</v>
+      </c>
+      <c r="G5" s="4">
+        <v>2000</v>
+      </c>
+      <c r="J5" s="4">
+        <v>1</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="L5" s="4">
+        <v>9600</v>
+      </c>
+      <c r="M5" s="4">
+        <v>8</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="O5" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19">
+      <c r="A6" s="4">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="C6" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="F1" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="L1" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="M1" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="N1" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="O1" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="P1" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q1" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17">
-      <c r="A2" s="3">
-        <f>devices!A2</f>
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F2" s="3">
-        <v>1000</v>
-      </c>
-      <c r="G2" s="3">
-        <v>1000</v>
-      </c>
-      <c r="L2" s="3">
-        <v>500000</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17">
-      <c r="A3" s="3">
-        <f>devices!A3</f>
+      <c r="D6" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="F6" s="4">
+        <v>2000</v>
+      </c>
+      <c r="G6" s="4">
+        <v>2000</v>
+      </c>
+      <c r="J6" s="4">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="F3" s="3">
-        <v>2000</v>
-      </c>
-      <c r="G3" s="3">
-        <v>1000</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="I3" s="3">
-        <v>33434</v>
-      </c>
-      <c r="J3" s="3">
+      <c r="K6" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="L6" s="4">
+        <v>9600</v>
+      </c>
+      <c r="M6" s="4">
+        <v>8</v>
+      </c>
+      <c r="N6" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="O6" s="4">
         <v>1</v>
       </c>
     </row>
@@ -2349,8 +1839,8 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultColWidth="9.11111111111111" defaultRowHeight="18" outlineLevelRow="5" outlineLevelCol="6"/>
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr defaultColWidth="9.11111111111111" defaultRowHeight="18" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="11.7619047619048" style="2" customWidth="1"/>
     <col min="2" max="2" width="20.6746031746032" style="2" customWidth="1"/>
@@ -2363,94 +1853,20 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C2" s="2" t="str">
-        <f>_xlfn.TEXTJOIN(",",TRUE,[2]遥测!$A$58:$A$71)</f>
-        <v>60,61,62,63,64,65,66,67,68,69,70,71</v>
-      </c>
-      <c r="D2" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C3" s="2" t="str">
-        <f>_xlfn.TEXTJOIN(",",TRUE,[2]遥测!$A$2:$A$55)</f>
-        <v>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23,24,25,26,27,28,29,30,31,32,33,34,35,36,40,41,42,43,44,45,46,47,48,49,50,51,52,53,54,55,56,57</v>
-      </c>
-      <c r="D3" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C4" s="2" t="str">
-        <f>_xlfn.TEXTJOIN(",",TRUE,[1]遥调!$A$2:$A$1000)</f>
-        <v>2000,2001,2002,2003,2004,2005,2006,2007,2008,2009,2010,2011,2012,2013,2014,2015,2016,2017,2018,2019,2020,2021,2022,2023,2024,2025,2026,2027,2028,2029,2030,2031,2032,2033,2034,2035,2036,2037,2038,2039,2040,2041,2042</v>
-      </c>
-      <c r="D4" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C5" s="2" t="str">
-        <f>_xlfn.TEXTJOIN(",",TRUE,[1]遥控!$A$2:$A$1000)</f>
-        <v>3000,3001,3002,3003,3004,3005,3006,3007,3008,3009,3010,3011,3012,3013,3014,3015</v>
-      </c>
-      <c r="D5" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D6" s="2">
-        <v>1</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/配置_v2.0.xlsx
+++ b/config/配置_v2.0.xlsx
@@ -1694,7 +1694,7 @@
         <v>2000</v>
       </c>
       <c r="G3" s="4">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="H3" s="6"/>
       <c r="I3" s="6"/>

--- a/config/配置_v2.0.xlsx
+++ b/config/配置_v2.0.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="18569" windowHeight="11268" activeTab="2"/>
+    <workbookView windowWidth="18569" windowHeight="11268"/>
   </bookViews>
   <sheets>
     <sheet name="project" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="94">
   <si>
     <t>key</t>
   </si>
@@ -59,6 +59,12 @@
     <t>项目名称：</t>
   </si>
   <si>
+    <t>emu_enable</t>
+  </si>
+  <si>
+    <t>是否启用EMU功能</t>
+  </si>
+  <si>
     <t>http_ip</t>
   </si>
   <si>
@@ -72,6 +78,12 @@
   </si>
   <si>
     <t>HTTP监听端口</t>
+  </si>
+  <si>
+    <t>mqtt_enable</t>
+  </si>
+  <si>
+    <t>是否启用MQTT</t>
   </si>
   <si>
     <t>mqtt_host</t>
@@ -1290,7 +1302,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr defaultColWidth="22.4047619047619" defaultRowHeight="18" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="22.4047619047619" style="4"/>
@@ -1335,19 +1347,19 @@
       <c r="A4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>10</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>12</v>
-      </c>
-      <c r="B5" s="4">
-        <v>9091</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>13</v>
@@ -1357,85 +1369,85 @@
       <c r="A6" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="4">
+        <v>9091</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>15</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="B7" s="4">
-        <v>1883</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="C8" s="4" t="s">
         <v>20</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="4">
+        <v>1883</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>22</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>31</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" s="4" t="s">
         <v>33</v>
-      </c>
-      <c r="B13" s="4">
-        <v>9092</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>34</v>
@@ -1446,10 +1458,32 @@
         <v>35</v>
       </c>
       <c r="B14" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C14" s="4" t="s">
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="4" t="s">
         <v>37</v>
+      </c>
+      <c r="B15" s="4">
+        <v>9092</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -1474,16 +1508,16 @@
   <sheetData>
     <row r="1" s="3" customFormat="1" spans="1:5">
       <c r="A1" s="3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E1" s="4"/>
     </row>
@@ -1492,13 +1526,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1506,13 +1540,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1520,13 +1554,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1534,13 +1568,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1548,13 +1582,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -1585,61 +1619,61 @@
   <sheetData>
     <row r="1" s="3" customFormat="1" spans="1:19">
       <c r="A1" s="3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="O1" s="5" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="P1" s="5" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="S1" s="3" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:19">
@@ -1647,16 +1681,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="F2" s="4">
         <v>2000</v>
@@ -1665,7 +1699,7 @@
         <v>2000</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="I2" s="4">
         <v>502</v>
@@ -1679,16 +1713,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F3" s="4">
         <v>2000</v>
@@ -1703,7 +1737,7 @@
         <v>500000</v>
       </c>
       <c r="P3" s="4" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -1711,16 +1745,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="F4" s="4">
         <v>2000</v>
@@ -1732,7 +1766,7 @@
         <v>2</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="L4" s="4">
         <v>9600</v>
@@ -1741,7 +1775,7 @@
         <v>8</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="O4" s="4">
         <v>1</v>
@@ -1752,16 +1786,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="F5" s="4">
         <v>2000</v>
@@ -1773,7 +1807,7 @@
         <v>1</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="L5" s="4">
         <v>9600</v>
@@ -1782,7 +1816,7 @@
         <v>8</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="O5" s="4">
         <v>1</v>
@@ -1793,16 +1827,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="F6" s="4">
         <v>2000</v>
@@ -1814,7 +1848,7 @@
         <v>1</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="L6" s="4">
         <v>9600</v>
@@ -1823,7 +1857,7 @@
         <v>8</v>
       </c>
       <c r="N6" s="4" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="O6" s="4">
         <v>1</v>
@@ -1853,16 +1887,16 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>

--- a/config/配置_v2.0.xlsx
+++ b/config/配置_v2.0.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="18569" windowHeight="11268"/>
+    <workbookView windowWidth="22010" windowHeight="12332" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="project" sheetId="1" r:id="rId1"/>
@@ -1693,7 +1693,7 @@
         <v>77</v>
       </c>
       <c r="F2" s="4">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="G2" s="4">
         <v>2000</v>

--- a/config/配置_v2.0.xlsx
+++ b/config/配置_v2.0.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="22010" windowHeight="12332" activeTab="2"/>
+    <workbookView windowWidth="22010" windowHeight="12332" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="project" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="98">
   <si>
     <t>key</t>
   </si>
@@ -215,6 +215,15 @@
     <t>消防系统</t>
   </si>
   <si>
+    <t>gpio</t>
+  </si>
+  <si>
+    <t>GPIO</t>
+  </si>
+  <si>
+    <t>DIDO</t>
+  </si>
+  <si>
     <t>comType</t>
   </si>
   <si>
@@ -300,6 +309,9 @@
   </si>
   <si>
     <t>/dev/ttyXRUSB2</t>
+  </si>
+  <si>
+    <t>./config/GPIO.xlsx</t>
   </si>
   <si>
     <t>device_id</t>
@@ -1496,8 +1508,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelRow="5" outlineLevelCol="4"/>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelRow="6" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="6.46031746031746" style="4" customWidth="1"/>
     <col min="2" max="2" width="20.9285714285714" style="4" customWidth="1"/>
@@ -1591,6 +1603,20 @@
         <v>60</v>
       </c>
     </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="6">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -1601,8 +1627,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:S6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelRow="5"/>
+  <dimension ref="A1:S7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelRow="6"/>
   <cols>
     <col min="1" max="1" width="6.46031746031746" style="4" customWidth="1"/>
     <col min="2" max="2" width="15.5952380952381" style="4" customWidth="1"/>
@@ -1628,52 +1654,52 @@
         <v>44</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="O1" s="5" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="P1" s="5" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="Q1" s="3" t="s">
         <v>45</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="S1" s="3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:19">
@@ -1687,10 +1713,10 @@
         <v>47</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F2" s="4">
         <v>1000</v>
@@ -1699,7 +1725,7 @@
         <v>2000</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="I2" s="4">
         <v>502</v>
@@ -1719,10 +1745,10 @@
         <v>50</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F3" s="4">
         <v>2000</v>
@@ -1737,7 +1763,7 @@
         <v>500000</v>
       </c>
       <c r="P3" s="4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -1751,10 +1777,10 @@
         <v>53</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F4" s="4">
         <v>2000</v>
@@ -1766,7 +1792,7 @@
         <v>2</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="L4" s="4">
         <v>9600</v>
@@ -1775,7 +1801,7 @@
         <v>8</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="O4" s="4">
         <v>1</v>
@@ -1792,10 +1818,10 @@
         <v>56</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F5" s="4">
         <v>2000</v>
@@ -1807,7 +1833,7 @@
         <v>1</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="L5" s="4">
         <v>9600</v>
@@ -1816,7 +1842,7 @@
         <v>8</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="O5" s="4">
         <v>1</v>
@@ -1833,10 +1859,10 @@
         <v>59</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F6" s="4">
         <v>2000</v>
@@ -1848,7 +1874,7 @@
         <v>1</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="L6" s="4">
         <v>9600</v>
@@ -1857,10 +1883,33 @@
         <v>8</v>
       </c>
       <c r="N6" s="4" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="O6" s="4">
         <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19">
+      <c r="A7" s="6">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="F7" s="4">
+        <v>2000</v>
+      </c>
+      <c r="G7" s="4">
+        <v>2000</v>
       </c>
     </row>
   </sheetData>
@@ -1887,16 +1936,16 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>

--- a/config/配置_v2.0.xlsx
+++ b/config/配置_v2.0.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="22010" windowHeight="12332" activeTab="1"/>
+    <workbookView windowWidth="22010" windowHeight="12332" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="project" sheetId="1" r:id="rId1"/>
